--- a/gstdatabase/GSTR-1-2022-2023.xlsx
+++ b/gstdatabase/GSTR-1-2022-2023.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jul-26\GST Statistics Downloads 31st Jul 26\Downloads\GSTR 1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Aug-26\GST Statistics Downloads 31st Aug 26\Downloads\GSTR 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8230C029-726B-4868-85D4-DD85D883443A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E866D7F8-886B-4F0A-9624-E9750D34BAEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1232,14 +1232,14 @@
       </c>
       <c r="E11" s="3">
         <f t="shared" ref="E11:E47" si="0">F11-D11</f>
-        <v>17927</v>
+        <v>17929</v>
       </c>
       <c r="F11" s="5">
-        <v>42556</v>
+        <v>42558</v>
       </c>
       <c r="G11" s="4">
         <f t="shared" ref="G11:G47" si="1">F11/C11</f>
-        <v>0.96011190325782869</v>
+        <v>0.96015702553921123</v>
       </c>
       <c r="H11" s="5">
         <v>45199</v>
@@ -1249,14 +1249,14 @@
       </c>
       <c r="J11" s="3">
         <f t="shared" ref="J11:J47" si="2">K11-I11</f>
-        <v>17716</v>
+        <v>17718</v>
       </c>
       <c r="K11" s="5">
-        <v>43482</v>
+        <v>43484</v>
       </c>
       <c r="L11" s="4">
         <f t="shared" ref="L11:L47" si="3">K11/H11</f>
-        <v>0.96201243390340496</v>
+        <v>0.96205668266997058</v>
       </c>
       <c r="M11" s="9">
         <v>98966</v>
@@ -1268,11 +1268,11 @@
         <v>95308</v>
       </c>
       <c r="P11" s="5">
-        <v>95539</v>
+        <v>95543</v>
       </c>
       <c r="Q11" s="4">
         <f t="shared" ref="Q11:Q47" si="4">P11/M11</f>
-        <v>0.96537194592082132</v>
+        <v>0.96541236384212759</v>
       </c>
       <c r="R11" s="5">
         <v>44504</v>
@@ -1282,14 +1282,14 @@
       </c>
       <c r="T11" s="3">
         <f t="shared" ref="T11:T47" si="5">U11-S11</f>
-        <v>17487</v>
+        <v>17490</v>
       </c>
       <c r="U11" s="5">
-        <v>42548</v>
+        <v>42551</v>
       </c>
       <c r="V11" s="4">
         <f t="shared" ref="V11:V47" si="6">U11/R11</f>
-        <v>0.95604889448139496</v>
+        <v>0.95611630415243576</v>
       </c>
       <c r="W11" s="5">
         <v>45023</v>
@@ -1299,14 +1299,14 @@
       </c>
       <c r="Y11" s="3">
         <f t="shared" ref="Y11:Y47" si="7">Z11-X11</f>
-        <v>19086</v>
+        <v>19089</v>
       </c>
       <c r="Z11" s="5">
-        <v>43352</v>
+        <v>43355</v>
       </c>
       <c r="AA11" s="4">
         <f t="shared" ref="AA11:AA47" si="8">Z11/W11</f>
-        <v>0.96288563623037116</v>
+        <v>0.96295226884037044</v>
       </c>
       <c r="AB11" s="5">
         <v>99888</v>
@@ -1316,14 +1316,14 @@
       </c>
       <c r="AD11" s="3">
         <f t="shared" ref="AD11:AD47" si="9">AE11-AC11</f>
-        <v>49061</v>
+        <v>49065</v>
       </c>
       <c r="AE11" s="5">
-        <v>97567</v>
+        <v>97571</v>
       </c>
       <c r="AF11" s="4">
         <f t="shared" ref="AF11:AF47" si="10">AE11/AB11</f>
-        <v>0.9767639756527311</v>
+        <v>0.97680402050296333</v>
       </c>
       <c r="AG11" s="5">
         <v>44744</v>
@@ -1333,14 +1333,14 @@
       </c>
       <c r="AI11" s="3">
         <f t="shared" ref="AI11:AI47" si="11">AJ11-AH11</f>
-        <v>16571</v>
+        <v>16574</v>
       </c>
       <c r="AJ11" s="5">
-        <v>43114</v>
+        <v>43117</v>
       </c>
       <c r="AK11" s="4">
         <f t="shared" ref="AK11:AK47" si="12">AJ11/AG11</f>
-        <v>0.96357053459681741</v>
+        <v>0.96363758269265154</v>
       </c>
       <c r="AL11" s="5">
         <v>45303</v>
@@ -1350,14 +1350,14 @@
       </c>
       <c r="AN11" s="3">
         <f t="shared" ref="AN11:AN47" si="13">AO11-AM11</f>
-        <v>17189</v>
+        <v>17192</v>
       </c>
       <c r="AO11" s="5">
-        <v>43684</v>
+        <v>43687</v>
       </c>
       <c r="AP11" s="4">
         <f t="shared" ref="AP11:AP47" si="14">AO11/AL11</f>
-        <v>0.96426285234973397</v>
+        <v>0.96432907312981475</v>
       </c>
       <c r="AQ11" s="3">
         <v>100769</v>
@@ -1367,14 +1367,14 @@
       </c>
       <c r="AS11" s="3">
         <f t="shared" ref="AS11:AS47" si="15">AT11-AR11</f>
-        <v>43289</v>
+        <v>43292</v>
       </c>
       <c r="AT11" s="3">
-        <v>98532</v>
+        <v>98535</v>
       </c>
       <c r="AU11" s="4">
         <f t="shared" ref="AU11:AU47" si="16">AT11/AQ11</f>
-        <v>0.97780071252071565</v>
+        <v>0.97783048358126012</v>
       </c>
       <c r="AV11" s="5">
         <v>46153</v>
@@ -1384,14 +1384,14 @@
       </c>
       <c r="AX11" s="3">
         <f t="shared" ref="AX11:AX47" si="17">AY11-AW11</f>
-        <v>14952</v>
+        <v>14955</v>
       </c>
       <c r="AY11" s="5">
-        <v>43457</v>
+        <v>43460</v>
       </c>
       <c r="AZ11" s="4">
         <f t="shared" ref="AZ11:AZ47" si="18">AY11/AV11</f>
-        <v>0.94158559573592182</v>
+        <v>0.94165059692761033</v>
       </c>
       <c r="BA11" s="10">
         <v>44735</v>
@@ -1401,14 +1401,14 @@
       </c>
       <c r="BC11" s="3">
         <f t="shared" ref="BC11:BC47" si="19">BD11-BB11</f>
-        <v>16369</v>
+        <v>16372</v>
       </c>
       <c r="BD11" s="5">
-        <v>44641</v>
+        <v>44644</v>
       </c>
       <c r="BE11" s="4">
         <f t="shared" ref="BE11:BE47" si="20">BD11/BA11</f>
-        <v>0.99789873700681797</v>
+        <v>0.99796579859170675</v>
       </c>
       <c r="BF11" s="10">
         <v>99991</v>
@@ -1418,14 +1418,14 @@
       </c>
       <c r="BH11" s="3">
         <f t="shared" ref="BH11:BH33" si="21">BI11-BG11</f>
-        <v>49944</v>
+        <v>49947</v>
       </c>
       <c r="BI11" s="5">
-        <v>100937</v>
+        <v>100940</v>
       </c>
       <c r="BJ11" s="4">
         <f t="shared" ref="BJ11:BJ33" si="22">BI11/BF11</f>
-        <v>1.009460851476633</v>
+        <v>1.0094908541768759</v>
       </c>
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.3">
@@ -1443,14 +1443,14 @@
       </c>
       <c r="E12" s="3">
         <f t="shared" si="0"/>
-        <v>34892</v>
+        <v>34894</v>
       </c>
       <c r="F12" s="5">
-        <v>154332</v>
+        <v>154334</v>
       </c>
       <c r="G12" s="4">
         <f t="shared" si="1"/>
-        <v>0.93616246906391032</v>
+        <v>0.93617460086378412</v>
       </c>
       <c r="H12" s="5">
         <v>167213</v>
@@ -1460,14 +1460,14 @@
       </c>
       <c r="J12" s="3">
         <f t="shared" si="2"/>
-        <v>33864</v>
+        <v>33868</v>
       </c>
       <c r="K12" s="5">
-        <v>157646</v>
+        <v>157650</v>
       </c>
       <c r="L12" s="4">
         <f t="shared" si="3"/>
-        <v>0.94278554897047473</v>
+        <v>0.942809470555519</v>
       </c>
       <c r="M12" s="9">
         <v>342449</v>
@@ -1479,11 +1479,11 @@
         <v>324491</v>
       </c>
       <c r="P12" s="5">
-        <v>324810</v>
+        <v>324815</v>
       </c>
       <c r="Q12" s="4">
         <f t="shared" si="4"/>
-        <v>0.94849160020908219</v>
+        <v>0.94850620092334914</v>
       </c>
       <c r="R12" s="5">
         <v>167538</v>
@@ -1493,14 +1493,14 @@
       </c>
       <c r="T12" s="3">
         <f t="shared" si="5"/>
-        <v>36315</v>
+        <v>36319</v>
       </c>
       <c r="U12" s="5">
-        <v>156769</v>
+        <v>156773</v>
       </c>
       <c r="V12" s="4">
         <f t="shared" si="6"/>
-        <v>0.93572204514796642</v>
+        <v>0.93574592032852244</v>
       </c>
       <c r="W12" s="5">
         <v>169859</v>
@@ -1510,14 +1510,14 @@
       </c>
       <c r="Y12" s="3">
         <f t="shared" si="7"/>
-        <v>38461</v>
+        <v>38465</v>
       </c>
       <c r="Z12" s="5">
-        <v>159341</v>
+        <v>159345</v>
       </c>
       <c r="AA12" s="4">
         <f t="shared" si="8"/>
-        <v>0.93807805297334845</v>
+        <v>0.93810160191688396</v>
       </c>
       <c r="AB12" s="5">
         <v>346997</v>
@@ -1527,14 +1527,14 @@
       </c>
       <c r="AD12" s="3">
         <f t="shared" si="9"/>
-        <v>94418</v>
+        <v>94423</v>
       </c>
       <c r="AE12" s="5">
-        <v>332063</v>
+        <v>332068</v>
       </c>
       <c r="AF12" s="4">
         <f t="shared" si="10"/>
-        <v>0.95696216393801681</v>
+        <v>0.95697657328449526</v>
       </c>
       <c r="AG12" s="5">
         <v>170493</v>
@@ -1544,14 +1544,14 @@
       </c>
       <c r="AI12" s="3">
         <f t="shared" si="11"/>
-        <v>34203</v>
+        <v>34207</v>
       </c>
       <c r="AJ12" s="5">
-        <v>160007</v>
+        <v>160011</v>
       </c>
       <c r="AK12" s="4">
         <f t="shared" si="12"/>
-        <v>0.93849600863378557</v>
+        <v>0.9385194700075663</v>
       </c>
       <c r="AL12" s="5">
         <v>172338</v>
@@ -1561,14 +1561,14 @@
       </c>
       <c r="AN12" s="3">
         <f t="shared" si="13"/>
-        <v>35481</v>
+        <v>35485</v>
       </c>
       <c r="AO12" s="5">
-        <v>162427</v>
+        <v>162431</v>
       </c>
       <c r="AP12" s="4">
         <f t="shared" si="14"/>
-        <v>0.94249091900799586</v>
+        <v>0.94251412921120126</v>
       </c>
       <c r="AQ12" s="3">
         <v>350104</v>
@@ -1578,14 +1578,14 @@
       </c>
       <c r="AS12" s="3">
         <f t="shared" si="15"/>
-        <v>82936</v>
+        <v>82941</v>
       </c>
       <c r="AT12" s="3">
-        <v>335795</v>
+        <v>335800</v>
       </c>
       <c r="AU12" s="4">
         <f t="shared" si="16"/>
-        <v>0.9591292872974887</v>
+        <v>0.95914356876813744</v>
       </c>
       <c r="AV12" s="5">
         <v>177002</v>
@@ -1595,14 +1595,14 @@
       </c>
       <c r="AX12" s="3">
         <f t="shared" si="17"/>
-        <v>29966</v>
+        <v>29970</v>
       </c>
       <c r="AY12" s="5">
-        <v>162050</v>
+        <v>162054</v>
       </c>
       <c r="AZ12" s="4">
         <f t="shared" si="18"/>
-        <v>0.9155263782330143</v>
+        <v>0.91554897684771919</v>
       </c>
       <c r="BA12" s="10">
         <v>166689</v>
@@ -1612,14 +1612,14 @@
       </c>
       <c r="BC12" s="3">
         <f t="shared" si="19"/>
-        <v>31826</v>
+        <v>31830</v>
       </c>
       <c r="BD12" s="5">
-        <v>164475</v>
+        <v>164479</v>
       </c>
       <c r="BE12" s="4">
         <f t="shared" si="20"/>
-        <v>0.98671777981750441</v>
+        <v>0.98674177660193529</v>
       </c>
       <c r="BF12" s="10">
         <v>341156</v>
@@ -1629,14 +1629,14 @@
       </c>
       <c r="BH12" s="3">
         <f t="shared" si="21"/>
-        <v>93920</v>
+        <v>93925</v>
       </c>
       <c r="BI12" s="5">
-        <v>340514</v>
+        <v>340519</v>
       </c>
       <c r="BJ12" s="4">
         <f t="shared" si="22"/>
-        <v>0.99811816295184608</v>
+        <v>0.99813281900362294</v>
       </c>
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.3">
@@ -1865,14 +1865,14 @@
       </c>
       <c r="E14" s="3">
         <f t="shared" si="0"/>
-        <v>34893</v>
+        <v>34895</v>
       </c>
       <c r="F14" s="5">
-        <v>77294</v>
+        <v>77296</v>
       </c>
       <c r="G14" s="4">
         <f t="shared" si="1"/>
-        <v>0.9335024154589372</v>
+        <v>0.93352657004830919</v>
       </c>
       <c r="H14" s="5">
         <v>84757</v>
@@ -1882,14 +1882,14 @@
       </c>
       <c r="J14" s="3">
         <f t="shared" si="2"/>
-        <v>34527</v>
+        <v>34528</v>
       </c>
       <c r="K14" s="5">
-        <v>79138</v>
+        <v>79139</v>
       </c>
       <c r="L14" s="4">
         <f t="shared" si="3"/>
-        <v>0.93370459077126378</v>
+        <v>0.93371638920679123</v>
       </c>
       <c r="M14" s="9">
         <v>154914</v>
@@ -1901,11 +1901,11 @@
         <v>144482</v>
       </c>
       <c r="P14" s="5">
-        <v>145051</v>
+        <v>145053</v>
       </c>
       <c r="Q14" s="4">
         <f t="shared" si="4"/>
-        <v>0.9363324166957151</v>
+        <v>0.93634532708470508</v>
       </c>
       <c r="R14" s="5">
         <v>85475</v>
@@ -1915,14 +1915,14 @@
       </c>
       <c r="T14" s="3">
         <f t="shared" si="5"/>
-        <v>36058</v>
+        <v>36060</v>
       </c>
       <c r="U14" s="5">
-        <v>78727</v>
+        <v>78729</v>
       </c>
       <c r="V14" s="4">
         <f t="shared" si="6"/>
-        <v>0.92105293945598132</v>
+        <v>0.92107633811055867</v>
       </c>
       <c r="W14" s="5">
         <v>86445</v>
@@ -1932,14 +1932,14 @@
       </c>
       <c r="Y14" s="3">
         <f t="shared" si="7"/>
-        <v>36740</v>
+        <v>36741</v>
       </c>
       <c r="Z14" s="5">
-        <v>80019</v>
+        <v>80020</v>
       </c>
       <c r="AA14" s="4">
         <f t="shared" si="8"/>
-        <v>0.92566371681415927</v>
+        <v>0.92567528486320783</v>
       </c>
       <c r="AB14" s="5">
         <v>156524</v>
@@ -2034,14 +2034,14 @@
       </c>
       <c r="BC14" s="3">
         <f t="shared" si="19"/>
-        <v>35291</v>
+        <v>35292</v>
       </c>
       <c r="BD14" s="5">
-        <v>85169</v>
+        <v>85170</v>
       </c>
       <c r="BE14" s="4">
         <f t="shared" si="20"/>
-        <v>0.98782170983193962</v>
+        <v>0.98783330820352822</v>
       </c>
       <c r="BF14" s="10">
         <v>155639</v>
@@ -2051,14 +2051,14 @@
       </c>
       <c r="BH14" s="3">
         <f t="shared" si="21"/>
-        <v>76843</v>
+        <v>76844</v>
       </c>
       <c r="BI14" s="5">
-        <v>155155</v>
+        <v>155156</v>
       </c>
       <c r="BJ14" s="4">
         <f t="shared" si="22"/>
-        <v>0.99689023959290413</v>
+        <v>0.9968966647177121</v>
       </c>
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.3">
@@ -2287,14 +2287,14 @@
       </c>
       <c r="E16" s="3">
         <f t="shared" si="0"/>
-        <v>106341</v>
+        <v>106342</v>
       </c>
       <c r="F16" s="5">
-        <v>390225</v>
+        <v>390226</v>
       </c>
       <c r="G16" s="4">
         <f t="shared" si="1"/>
-        <v>0.95111411175727911</v>
+        <v>0.95111654910524956</v>
       </c>
       <c r="H16" s="5">
         <v>416018</v>
@@ -2304,14 +2304,14 @@
       </c>
       <c r="J16" s="3">
         <f t="shared" si="2"/>
-        <v>103647</v>
+        <v>103648</v>
       </c>
       <c r="K16" s="5">
-        <v>398188</v>
+        <v>398189</v>
       </c>
       <c r="L16" s="4">
         <f t="shared" si="3"/>
-        <v>0.95714127754087563</v>
+        <v>0.95714368128302141</v>
       </c>
       <c r="M16" s="9">
         <v>750813</v>
@@ -2323,11 +2323,11 @@
         <v>716590</v>
       </c>
       <c r="P16" s="5">
-        <v>718013</v>
+        <v>718017</v>
       </c>
       <c r="Q16" s="4">
         <f t="shared" si="4"/>
-        <v>0.95631402226652973</v>
+        <v>0.95631934982478994</v>
       </c>
       <c r="R16" s="5">
         <v>419109</v>
@@ -2337,14 +2337,14 @@
       </c>
       <c r="T16" s="3">
         <f t="shared" si="5"/>
-        <v>111554</v>
+        <v>111555</v>
       </c>
       <c r="U16" s="5">
-        <v>399097</v>
+        <v>399098</v>
       </c>
       <c r="V16" s="4">
         <f t="shared" si="6"/>
-        <v>0.95225108503992995</v>
+        <v>0.95225347105406943</v>
       </c>
       <c r="W16" s="5">
         <v>423539</v>
@@ -2354,14 +2354,14 @@
       </c>
       <c r="Y16" s="3">
         <f t="shared" si="7"/>
-        <v>110440</v>
+        <v>110441</v>
       </c>
       <c r="Z16" s="5">
-        <v>405280</v>
+        <v>405281</v>
       </c>
       <c r="AA16" s="4">
         <f t="shared" si="8"/>
-        <v>0.95688944819721444</v>
+        <v>0.95689180925487383</v>
       </c>
       <c r="AB16" s="5">
         <v>762171</v>
@@ -2371,14 +2371,14 @@
       </c>
       <c r="AD16" s="3">
         <f t="shared" si="9"/>
-        <v>204098</v>
+        <v>204102</v>
       </c>
       <c r="AE16" s="5">
-        <v>732832</v>
+        <v>732836</v>
       </c>
       <c r="AF16" s="4">
         <f t="shared" si="10"/>
-        <v>0.96150601374232292</v>
+        <v>0.96151126190841685</v>
       </c>
       <c r="AG16" s="5">
         <v>429452</v>
@@ -2388,14 +2388,14 @@
       </c>
       <c r="AI16" s="3">
         <f t="shared" si="11"/>
-        <v>106282</v>
+        <v>106284</v>
       </c>
       <c r="AJ16" s="5">
-        <v>410507</v>
+        <v>410509</v>
       </c>
       <c r="AK16" s="4">
         <f t="shared" si="12"/>
-        <v>0.95588564030438794</v>
+        <v>0.95589029740227083</v>
       </c>
       <c r="AL16" s="5">
         <v>434676</v>
@@ -2405,14 +2405,14 @@
       </c>
       <c r="AN16" s="3">
         <f t="shared" si="13"/>
-        <v>110274</v>
+        <v>110278</v>
       </c>
       <c r="AO16" s="5">
-        <v>416385</v>
+        <v>416389</v>
       </c>
       <c r="AP16" s="4">
         <f t="shared" si="14"/>
-        <v>0.95792038207768548</v>
+        <v>0.95792958433407871</v>
       </c>
       <c r="AQ16" s="3">
         <v>772632</v>
@@ -2422,14 +2422,14 @@
       </c>
       <c r="AS16" s="3">
         <f t="shared" si="15"/>
-        <v>180850</v>
+        <v>180857</v>
       </c>
       <c r="AT16" s="3">
-        <v>743494</v>
+        <v>743501</v>
       </c>
       <c r="AU16" s="4">
         <f t="shared" si="16"/>
-        <v>0.9622873502521252</v>
+        <v>0.96229641019269196</v>
       </c>
       <c r="AV16" s="5">
         <v>448203</v>
@@ -2439,14 +2439,14 @@
       </c>
       <c r="AX16" s="3">
         <f t="shared" si="17"/>
-        <v>98410</v>
+        <v>98415</v>
       </c>
       <c r="AY16" s="5">
-        <v>418489</v>
+        <v>418494</v>
       </c>
       <c r="AZ16" s="4">
         <f t="shared" si="18"/>
-        <v>0.93370414745104335</v>
+        <v>0.93371530311042095</v>
       </c>
       <c r="BA16" s="10">
         <v>429555</v>
@@ -2456,14 +2456,14 @@
       </c>
       <c r="BC16" s="3">
         <f t="shared" si="19"/>
-        <v>103432</v>
+        <v>103437</v>
       </c>
       <c r="BD16" s="5">
-        <v>424706</v>
+        <v>424711</v>
       </c>
       <c r="BE16" s="4">
         <f t="shared" si="20"/>
-        <v>0.98871157360524264</v>
+        <v>0.98872321355821724</v>
       </c>
       <c r="BF16" s="10">
         <v>753579</v>
@@ -2473,14 +2473,14 @@
       </c>
       <c r="BH16" s="3">
         <f t="shared" si="21"/>
-        <v>197250</v>
+        <v>197259</v>
       </c>
       <c r="BI16" s="5">
-        <v>753334</v>
+        <v>753343</v>
       </c>
       <c r="BJ16" s="4">
         <f t="shared" si="22"/>
-        <v>0.99967488478314814</v>
+        <v>0.99968682779111417</v>
       </c>
     </row>
     <row r="17" spans="1:62" x14ac:dyDescent="0.3">
@@ -2498,14 +2498,14 @@
       </c>
       <c r="E17" s="3">
         <f t="shared" si="0"/>
-        <v>97180</v>
+        <v>97183</v>
       </c>
       <c r="F17" s="5">
-        <v>273158</v>
+        <v>273161</v>
       </c>
       <c r="G17" s="4">
         <f t="shared" si="1"/>
-        <v>0.96566279328739957</v>
+        <v>0.96567339882844128</v>
       </c>
       <c r="H17" s="5">
         <v>290053</v>
@@ -2515,14 +2515,14 @@
       </c>
       <c r="J17" s="3">
         <f t="shared" si="2"/>
-        <v>89059</v>
+        <v>89063</v>
       </c>
       <c r="K17" s="5">
-        <v>281350</v>
+        <v>281354</v>
       </c>
       <c r="L17" s="4">
         <f t="shared" si="3"/>
-        <v>0.96999513881945709</v>
+        <v>0.97000892940255745</v>
       </c>
       <c r="M17" s="9">
         <v>666005</v>
@@ -2534,11 +2534,11 @@
         <v>640256</v>
       </c>
       <c r="P17" s="5">
-        <v>641511</v>
+        <v>641517</v>
       </c>
       <c r="Q17" s="4">
         <f t="shared" si="4"/>
-        <v>0.96322249832959217</v>
+        <v>0.9632315072709664</v>
       </c>
       <c r="R17" s="5">
         <v>287981</v>
@@ -2548,14 +2548,14 @@
       </c>
       <c r="T17" s="3">
         <f t="shared" si="5"/>
-        <v>96348</v>
+        <v>96352</v>
       </c>
       <c r="U17" s="5">
-        <v>276620</v>
+        <v>276624</v>
       </c>
       <c r="V17" s="4">
         <f t="shared" si="6"/>
-        <v>0.96054948069490698</v>
+        <v>0.96056337050013718</v>
       </c>
       <c r="W17" s="5">
         <v>293004</v>
@@ -2565,14 +2565,14 @@
       </c>
       <c r="Y17" s="3">
         <f t="shared" si="7"/>
-        <v>99058</v>
+        <v>99064</v>
       </c>
       <c r="Z17" s="5">
-        <v>283324</v>
+        <v>283330</v>
       </c>
       <c r="AA17" s="4">
         <f t="shared" si="8"/>
-        <v>0.96696290835619991</v>
+        <v>0.96698338589234278</v>
       </c>
       <c r="AB17" s="5">
         <v>677720</v>
@@ -2582,14 +2582,14 @@
       </c>
       <c r="AD17" s="3">
         <f t="shared" si="9"/>
-        <v>263397</v>
+        <v>263400</v>
       </c>
       <c r="AE17" s="5">
-        <v>660032</v>
+        <v>660035</v>
       </c>
       <c r="AF17" s="4">
         <f t="shared" si="10"/>
-        <v>0.97390072596352473</v>
+        <v>0.97390515257038301</v>
       </c>
       <c r="AG17" s="5">
         <v>295677</v>
@@ -2599,14 +2599,14 @@
       </c>
       <c r="AI17" s="3">
         <f t="shared" si="11"/>
-        <v>86966</v>
+        <v>86968</v>
       </c>
       <c r="AJ17" s="5">
-        <v>286417</v>
+        <v>286419</v>
       </c>
       <c r="AK17" s="4">
         <f t="shared" si="12"/>
-        <v>0.96868204155209903</v>
+        <v>0.96868880568999283</v>
       </c>
       <c r="AL17" s="5">
         <v>303084</v>
@@ -2616,14 +2616,14 @@
       </c>
       <c r="AN17" s="3">
         <f t="shared" si="13"/>
-        <v>89244</v>
+        <v>89246</v>
       </c>
       <c r="AO17" s="5">
-        <v>294601</v>
+        <v>294603</v>
       </c>
       <c r="AP17" s="4">
         <f t="shared" si="14"/>
-        <v>0.97201105964023171</v>
+        <v>0.97201765847091892</v>
       </c>
       <c r="AQ17" s="3">
         <v>690105</v>
@@ -2633,14 +2633,14 @@
       </c>
       <c r="AS17" s="3">
         <f t="shared" si="15"/>
-        <v>218609</v>
+        <v>218613</v>
       </c>
       <c r="AT17" s="3">
-        <v>674490</v>
+        <v>674494</v>
       </c>
       <c r="AU17" s="4">
         <f t="shared" si="16"/>
-        <v>0.97737300845523511</v>
+        <v>0.97737880467465099</v>
       </c>
       <c r="AV17" s="5">
         <v>311697</v>
@@ -2650,14 +2650,14 @@
       </c>
       <c r="AX17" s="3">
         <f t="shared" si="17"/>
-        <v>74902</v>
+        <v>74905</v>
       </c>
       <c r="AY17" s="5">
-        <v>292920</v>
+        <v>292923</v>
       </c>
       <c r="AZ17" s="4">
         <f t="shared" si="18"/>
-        <v>0.93975880422333224</v>
+        <v>0.93976842895504287</v>
       </c>
       <c r="BA17" s="10">
         <v>307540</v>
@@ -2667,14 +2667,14 @@
       </c>
       <c r="BC17" s="3">
         <f t="shared" si="19"/>
-        <v>81878</v>
+        <v>81880</v>
       </c>
       <c r="BD17" s="5">
-        <v>300846</v>
+        <v>300848</v>
       </c>
       <c r="BE17" s="4">
         <f t="shared" si="20"/>
-        <v>0.97823372569421863</v>
+        <v>0.97824022891331208</v>
       </c>
       <c r="BF17" s="10">
         <v>689646</v>
@@ -2684,14 +2684,14 @@
       </c>
       <c r="BH17" s="3">
         <f t="shared" si="21"/>
-        <v>257521</v>
+        <v>257525</v>
       </c>
       <c r="BI17" s="5">
-        <v>688761</v>
+        <v>688765</v>
       </c>
       <c r="BJ17" s="4">
         <f t="shared" si="22"/>
-        <v>0.99871673293254803</v>
+        <v>0.99872253300968905</v>
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.3">
@@ -2709,14 +2709,14 @@
       </c>
       <c r="E18" s="3">
         <f t="shared" si="0"/>
-        <v>397894</v>
+        <v>397895</v>
       </c>
       <c r="F18" s="5">
-        <v>804257</v>
+        <v>804258</v>
       </c>
       <c r="G18" s="4">
         <f t="shared" si="1"/>
-        <v>0.95688037701413087</v>
+        <v>0.95688156678354164</v>
       </c>
       <c r="H18" s="5">
         <v>861805</v>
@@ -2726,14 +2726,14 @@
       </c>
       <c r="J18" s="3">
         <f t="shared" si="2"/>
-        <v>381254</v>
+        <v>381256</v>
       </c>
       <c r="K18" s="5">
-        <v>819371</v>
+        <v>819373</v>
       </c>
       <c r="L18" s="4">
         <f t="shared" si="3"/>
-        <v>0.9507614831661455</v>
+        <v>0.95076380387674708</v>
       </c>
       <c r="M18" s="9">
         <v>1358945</v>
@@ -2745,11 +2745,11 @@
         <v>1272521</v>
       </c>
       <c r="P18" s="5">
-        <v>1276388</v>
+        <v>1276391</v>
       </c>
       <c r="Q18" s="4">
         <f t="shared" si="4"/>
-        <v>0.93924919698736886</v>
+        <v>0.93925140458223111</v>
       </c>
       <c r="R18" s="5">
         <v>869959</v>
@@ -2759,14 +2759,14 @@
       </c>
       <c r="T18" s="3">
         <f t="shared" si="5"/>
-        <v>402929</v>
+        <v>402931</v>
       </c>
       <c r="U18" s="5">
-        <v>822389</v>
+        <v>822391</v>
       </c>
       <c r="V18" s="4">
         <f t="shared" si="6"/>
-        <v>0.94531926217212536</v>
+        <v>0.94532156113104182</v>
       </c>
       <c r="W18" s="5">
         <v>883450</v>
@@ -2776,14 +2776,14 @@
       </c>
       <c r="Y18" s="3">
         <f t="shared" si="7"/>
-        <v>412767</v>
+        <v>412772</v>
       </c>
       <c r="Z18" s="5">
-        <v>838163</v>
+        <v>838168</v>
       </c>
       <c r="AA18" s="4">
         <f t="shared" si="8"/>
-        <v>0.94873846850415988</v>
+        <v>0.94874412813401998</v>
       </c>
       <c r="AB18" s="5">
         <v>1397129</v>
@@ -2793,14 +2793,14 @@
       </c>
       <c r="AD18" s="3">
         <f t="shared" si="9"/>
-        <v>718469</v>
+        <v>718472</v>
       </c>
       <c r="AE18" s="5">
-        <v>1341464</v>
+        <v>1341467</v>
       </c>
       <c r="AF18" s="4">
         <f t="shared" si="10"/>
-        <v>0.9601575802950193</v>
+        <v>0.9601597275555801</v>
       </c>
       <c r="AG18" s="5">
         <v>899515</v>
@@ -2810,14 +2810,14 @@
       </c>
       <c r="AI18" s="3">
         <f t="shared" si="11"/>
-        <v>400336</v>
+        <v>400340</v>
       </c>
       <c r="AJ18" s="5">
-        <v>863735</v>
+        <v>863739</v>
       </c>
       <c r="AK18" s="4">
         <f t="shared" si="12"/>
-        <v>0.96022300906599667</v>
+        <v>0.96022745590679426</v>
       </c>
       <c r="AL18" s="5">
         <v>914748</v>
@@ -2827,14 +2827,14 @@
       </c>
       <c r="AN18" s="3">
         <f t="shared" si="13"/>
-        <v>398139</v>
+        <v>398143</v>
       </c>
       <c r="AO18" s="5">
-        <v>880116</v>
+        <v>880120</v>
       </c>
       <c r="AP18" s="4">
         <f t="shared" si="14"/>
-        <v>0.96214039276390873</v>
+        <v>0.96214476555291728</v>
       </c>
       <c r="AQ18" s="3">
         <v>1436617</v>
@@ -2844,14 +2844,14 @@
       </c>
       <c r="AS18" s="3">
         <f t="shared" si="15"/>
-        <v>655876</v>
+        <v>655878</v>
       </c>
       <c r="AT18" s="3">
-        <v>1378615</v>
+        <v>1378617</v>
       </c>
       <c r="AU18" s="4">
         <f t="shared" si="16"/>
-        <v>0.95962598242955499</v>
+        <v>0.9596273745890519</v>
       </c>
       <c r="AV18" s="5">
         <v>954168</v>
@@ -2861,14 +2861,14 @@
       </c>
       <c r="AX18" s="3">
         <f t="shared" si="17"/>
-        <v>385910</v>
+        <v>385912</v>
       </c>
       <c r="AY18" s="5">
-        <v>893004</v>
+        <v>893006</v>
       </c>
       <c r="AZ18" s="4">
         <f t="shared" si="18"/>
-        <v>0.9358980808411097</v>
+        <v>0.93590017690804972</v>
       </c>
       <c r="BA18" s="10">
         <v>922519</v>
@@ -2878,14 +2878,14 @@
       </c>
       <c r="BC18" s="3">
         <f t="shared" si="19"/>
-        <v>429138</v>
+        <v>429140</v>
       </c>
       <c r="BD18" s="5">
-        <v>910838</v>
+        <v>910840</v>
       </c>
       <c r="BE18" s="4">
         <f t="shared" si="20"/>
-        <v>0.98733793016729199</v>
+        <v>0.98734009814432011</v>
       </c>
       <c r="BF18" s="10">
         <v>1428140</v>
@@ -2895,14 +2895,14 @@
       </c>
       <c r="BH18" s="3">
         <f t="shared" si="21"/>
-        <v>725133</v>
+        <v>725135</v>
       </c>
       <c r="BI18" s="5">
-        <v>1417116</v>
+        <v>1417118</v>
       </c>
       <c r="BJ18" s="4">
         <f t="shared" si="22"/>
-        <v>0.99228086882238431</v>
+        <v>0.99228226924531204</v>
       </c>
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.3">
@@ -2920,14 +2920,14 @@
       </c>
       <c r="E19" s="3">
         <f t="shared" si="0"/>
-        <v>162685</v>
+        <v>162687</v>
       </c>
       <c r="F19" s="5">
-        <v>236286</v>
+        <v>236288</v>
       </c>
       <c r="G19" s="4">
         <f t="shared" si="1"/>
-        <v>0.85470895489994647</v>
+        <v>0.85471618942890626</v>
       </c>
       <c r="H19" s="5">
         <v>280982</v>
@@ -2937,14 +2937,14 @@
       </c>
       <c r="J19" s="3">
         <f t="shared" si="2"/>
-        <v>160631</v>
+        <v>160634</v>
       </c>
       <c r="K19" s="5">
-        <v>240914</v>
+        <v>240917</v>
       </c>
       <c r="L19" s="4">
         <f t="shared" si="3"/>
-        <v>0.85740011815703498</v>
+        <v>0.85741079499754436</v>
       </c>
       <c r="M19" s="9">
         <v>470659</v>
@@ -2956,11 +2956,11 @@
         <v>406179</v>
       </c>
       <c r="P19" s="5">
-        <v>408679</v>
+        <v>408681</v>
       </c>
       <c r="Q19" s="4">
         <f t="shared" si="4"/>
-        <v>0.86831230253750591</v>
+        <v>0.86831655189850832</v>
       </c>
       <c r="R19" s="5">
         <v>282327</v>
@@ -2970,14 +2970,14 @@
       </c>
       <c r="T19" s="3">
         <f t="shared" si="5"/>
-        <v>164077</v>
+        <v>164079</v>
       </c>
       <c r="U19" s="5">
-        <v>240715</v>
+        <v>240717</v>
       </c>
       <c r="V19" s="4">
         <f t="shared" si="6"/>
-        <v>0.85261062526786313</v>
+        <v>0.8526177092520375</v>
       </c>
       <c r="W19" s="5">
         <v>286093</v>
@@ -2987,14 +2987,14 @@
       </c>
       <c r="Y19" s="3">
         <f t="shared" si="7"/>
-        <v>167498</v>
+        <v>167500</v>
       </c>
       <c r="Z19" s="5">
-        <v>245971</v>
+        <v>245973</v>
       </c>
       <c r="AA19" s="4">
         <f t="shared" si="8"/>
-        <v>0.85975888959184599</v>
+        <v>0.8597658803256284</v>
       </c>
       <c r="AB19" s="5">
         <v>481143</v>
@@ -3004,14 +3004,14 @@
       </c>
       <c r="AD19" s="3">
         <f t="shared" si="9"/>
-        <v>316663</v>
+        <v>316666</v>
       </c>
       <c r="AE19" s="5">
-        <v>436098</v>
+        <v>436101</v>
       </c>
       <c r="AF19" s="4">
         <f t="shared" si="10"/>
-        <v>0.90637918456675037</v>
+        <v>0.90638541971929343</v>
       </c>
       <c r="AG19" s="5">
         <v>287213</v>
@@ -3021,14 +3021,14 @@
       </c>
       <c r="AI19" s="3">
         <f t="shared" si="11"/>
-        <v>164982</v>
+        <v>164986</v>
       </c>
       <c r="AJ19" s="5">
-        <v>254432</v>
+        <v>254436</v>
       </c>
       <c r="AK19" s="4">
         <f t="shared" si="12"/>
-        <v>0.88586519412422138</v>
+        <v>0.8858791210704251</v>
       </c>
       <c r="AL19" s="5">
         <v>292666</v>
@@ -3038,14 +3038,14 @@
       </c>
       <c r="AN19" s="3">
         <f t="shared" si="13"/>
-        <v>159540</v>
+        <v>159545</v>
       </c>
       <c r="AO19" s="5">
-        <v>260136</v>
+        <v>260141</v>
       </c>
       <c r="AP19" s="4">
         <f t="shared" si="14"/>
-        <v>0.88884940512392963</v>
+        <v>0.88886648944530622</v>
       </c>
       <c r="AQ19" s="3">
         <v>495564</v>
@@ -3055,14 +3055,14 @@
       </c>
       <c r="AS19" s="3">
         <f t="shared" si="15"/>
-        <v>290910</v>
+        <v>290915</v>
       </c>
       <c r="AT19" s="3">
-        <v>448270</v>
+        <v>448275</v>
       </c>
       <c r="AU19" s="4">
         <f t="shared" si="16"/>
-        <v>0.90456530337151209</v>
+        <v>0.90457539288568178</v>
       </c>
       <c r="AV19" s="5">
         <v>310298</v>
@@ -3072,14 +3072,14 @@
       </c>
       <c r="AX19" s="3">
         <f t="shared" si="17"/>
-        <v>162871</v>
+        <v>162875</v>
       </c>
       <c r="AY19" s="5">
-        <v>263970</v>
+        <v>263974</v>
       </c>
       <c r="AZ19" s="4">
         <f t="shared" si="18"/>
-        <v>0.85069836093046036</v>
+        <v>0.85071125176443285</v>
       </c>
       <c r="BA19" s="10">
         <v>280202</v>
@@ -3089,14 +3089,14 @@
       </c>
       <c r="BC19" s="3">
         <f t="shared" si="19"/>
-        <v>182669</v>
+        <v>182673</v>
       </c>
       <c r="BD19" s="5">
-        <v>272738</v>
+        <v>272742</v>
       </c>
       <c r="BE19" s="4">
         <f t="shared" si="20"/>
-        <v>0.97336207450339396</v>
+        <v>0.97337634991898703</v>
       </c>
       <c r="BF19" s="10">
         <v>473091</v>
@@ -3106,14 +3106,14 @@
       </c>
       <c r="BH19" s="3">
         <f t="shared" si="21"/>
-        <v>327689</v>
+        <v>327694</v>
       </c>
       <c r="BI19" s="5">
-        <v>464753</v>
+        <v>464758</v>
       </c>
       <c r="BJ19" s="4">
         <f t="shared" si="22"/>
-        <v>0.98237548378641737</v>
+        <v>0.98238605257762246</v>
       </c>
     </row>
     <row r="20" spans="1:62" x14ac:dyDescent="0.3">
@@ -3249,14 +3249,14 @@
       </c>
       <c r="AN20" s="3">
         <f t="shared" si="13"/>
-        <v>3253</v>
+        <v>3254</v>
       </c>
       <c r="AO20" s="5">
-        <v>5548</v>
+        <v>5549</v>
       </c>
       <c r="AP20" s="4">
         <f t="shared" si="14"/>
-        <v>0.86068879925535213</v>
+        <v>0.86084393422277383</v>
       </c>
       <c r="AQ20" s="3">
         <v>9604</v>
@@ -3266,14 +3266,14 @@
       </c>
       <c r="AS20" s="3">
         <f t="shared" si="15"/>
-        <v>5299</v>
+        <v>5300</v>
       </c>
       <c r="AT20" s="3">
-        <v>8628</v>
+        <v>8629</v>
       </c>
       <c r="AU20" s="4">
         <f t="shared" si="16"/>
-        <v>0.89837567680133279</v>
+        <v>0.89847980008329864</v>
       </c>
       <c r="AV20" s="5">
         <v>6642</v>
@@ -3283,14 +3283,14 @@
       </c>
       <c r="AX20" s="3">
         <f t="shared" si="17"/>
-        <v>3119</v>
+        <v>3120</v>
       </c>
       <c r="AY20" s="5">
-        <v>5607</v>
+        <v>5608</v>
       </c>
       <c r="AZ20" s="4">
         <f t="shared" si="18"/>
-        <v>0.84417344173441733</v>
+        <v>0.84432399879554354</v>
       </c>
       <c r="BA20" s="10">
         <v>5628</v>
@@ -3300,14 +3300,14 @@
       </c>
       <c r="BC20" s="3">
         <f t="shared" si="19"/>
-        <v>3329</v>
+        <v>3330</v>
       </c>
       <c r="BD20" s="5">
-        <v>5722</v>
+        <v>5723</v>
       </c>
       <c r="BE20" s="4">
         <f t="shared" si="20"/>
-        <v>1.0167022032693676</v>
+        <v>1.0168798862828714</v>
       </c>
       <c r="BF20" s="10">
         <v>8802</v>
@@ -3317,14 +3317,14 @@
       </c>
       <c r="BH20" s="3">
         <f t="shared" si="21"/>
-        <v>5783</v>
+        <v>5784</v>
       </c>
       <c r="BI20" s="5">
-        <v>8971</v>
+        <v>8972</v>
       </c>
       <c r="BJ20" s="4">
         <f t="shared" si="22"/>
-        <v>1.019200181776869</v>
+        <v>1.0193137923199274</v>
       </c>
     </row>
     <row r="21" spans="1:62" x14ac:dyDescent="0.3">
@@ -3342,14 +3342,14 @@
       </c>
       <c r="E21" s="3">
         <f t="shared" si="0"/>
-        <v>6074</v>
+        <v>6075</v>
       </c>
       <c r="F21" s="5">
-        <v>8309</v>
+        <v>8310</v>
       </c>
       <c r="G21" s="4">
         <f t="shared" si="1"/>
-        <v>0.78261279080719603</v>
+        <v>0.78270697937270417</v>
       </c>
       <c r="H21" s="5">
         <v>10811</v>
@@ -3359,14 +3359,14 @@
       </c>
       <c r="J21" s="3">
         <f t="shared" si="2"/>
-        <v>5873</v>
+        <v>5874</v>
       </c>
       <c r="K21" s="5">
-        <v>8436</v>
+        <v>8437</v>
       </c>
       <c r="L21" s="4">
         <f t="shared" si="3"/>
-        <v>0.78031634446397191</v>
+        <v>0.78040884284525025</v>
       </c>
       <c r="M21" s="9">
         <v>14133</v>
@@ -3378,11 +3378,11 @@
         <v>11192</v>
       </c>
       <c r="P21" s="5">
-        <v>11404</v>
+        <v>11405</v>
       </c>
       <c r="Q21" s="4">
         <f t="shared" si="4"/>
-        <v>0.80690582325054838</v>
+        <v>0.8069765796363122</v>
       </c>
       <c r="R21" s="5">
         <v>11019</v>
@@ -3392,14 +3392,14 @@
       </c>
       <c r="T21" s="3">
         <f t="shared" si="5"/>
-        <v>6089</v>
+        <v>6090</v>
       </c>
       <c r="U21" s="5">
-        <v>8631</v>
+        <v>8632</v>
       </c>
       <c r="V21" s="4">
         <f t="shared" si="6"/>
-        <v>0.78328341954805336</v>
+        <v>0.78337417188492608</v>
       </c>
       <c r="W21" s="5">
         <v>11175</v>
@@ -3409,14 +3409,14 @@
       </c>
       <c r="Y21" s="3">
         <f t="shared" si="7"/>
-        <v>6286</v>
+        <v>6287</v>
       </c>
       <c r="Z21" s="5">
-        <v>8802</v>
+        <v>8803</v>
       </c>
       <c r="AA21" s="4">
         <f t="shared" si="8"/>
-        <v>0.78765100671140942</v>
+        <v>0.7877404921700224</v>
       </c>
       <c r="AB21" s="5">
         <v>14571</v>
@@ -3426,14 +3426,14 @@
       </c>
       <c r="AD21" s="3">
         <f t="shared" si="9"/>
-        <v>9108</v>
+        <v>9109</v>
       </c>
       <c r="AE21" s="5">
-        <v>12225</v>
+        <v>12226</v>
       </c>
       <c r="AF21" s="4">
         <f t="shared" si="10"/>
-        <v>0.83899526456660489</v>
+        <v>0.83906389403609916</v>
       </c>
       <c r="AG21" s="5">
         <v>11345</v>
@@ -3443,14 +3443,14 @@
       </c>
       <c r="AI21" s="3">
         <f t="shared" si="11"/>
-        <v>6297</v>
+        <v>6299</v>
       </c>
       <c r="AJ21" s="5">
-        <v>9225</v>
+        <v>9227</v>
       </c>
       <c r="AK21" s="4">
         <f t="shared" si="12"/>
-        <v>0.81313353900396645</v>
+        <v>0.8133098281181137</v>
       </c>
       <c r="AL21" s="5">
         <v>11441</v>
@@ -3460,14 +3460,14 @@
       </c>
       <c r="AN21" s="3">
         <f t="shared" si="13"/>
-        <v>6144</v>
+        <v>6147</v>
       </c>
       <c r="AO21" s="5">
-        <v>9336</v>
+        <v>9339</v>
       </c>
       <c r="AP21" s="4">
         <f t="shared" si="14"/>
-        <v>0.81601258631238527</v>
+        <v>0.81627480115374529</v>
       </c>
       <c r="AQ21" s="3">
         <v>14790</v>
@@ -3477,14 +3477,14 @@
       </c>
       <c r="AS21" s="3">
         <f t="shared" si="15"/>
-        <v>8844</v>
+        <v>8847</v>
       </c>
       <c r="AT21" s="3">
-        <v>12534</v>
+        <v>12537</v>
       </c>
       <c r="AU21" s="4">
         <f t="shared" si="16"/>
-        <v>0.84746450304259635</v>
+        <v>0.84766734279918865</v>
       </c>
       <c r="AV21" s="5">
         <v>11740</v>
@@ -3494,14 +3494,14 @@
       </c>
       <c r="AX21" s="3">
         <f t="shared" si="17"/>
-        <v>6332</v>
+        <v>6335</v>
       </c>
       <c r="AY21" s="5">
-        <v>9477</v>
+        <v>9480</v>
       </c>
       <c r="AZ21" s="4">
         <f t="shared" si="18"/>
-        <v>0.80724020442930156</v>
+        <v>0.80749574105621802</v>
       </c>
       <c r="BA21" s="10">
         <v>9242</v>
@@ -3511,14 +3511,14 @@
       </c>
       <c r="BC21" s="3">
         <f t="shared" si="19"/>
-        <v>6595</v>
+        <v>6598</v>
       </c>
       <c r="BD21" s="5">
-        <v>9586</v>
+        <v>9589</v>
       </c>
       <c r="BE21" s="4">
         <f t="shared" si="20"/>
-        <v>1.0372213806535382</v>
+        <v>1.0375459857173772</v>
       </c>
       <c r="BF21" s="10">
         <v>12544</v>
@@ -3528,14 +3528,14 @@
       </c>
       <c r="BH21" s="3">
         <f t="shared" si="21"/>
-        <v>9740</v>
+        <v>9743</v>
       </c>
       <c r="BI21" s="5">
-        <v>12931</v>
+        <v>12934</v>
       </c>
       <c r="BJ21" s="4">
         <f t="shared" si="22"/>
-        <v>1.0308514030612246</v>
+        <v>1.0310905612244898</v>
       </c>
     </row>
     <row r="22" spans="1:62" x14ac:dyDescent="0.3">
@@ -3553,14 +3553,14 @@
       </c>
       <c r="E22" s="3">
         <f t="shared" si="0"/>
-        <v>3777</v>
+        <v>3778</v>
       </c>
       <c r="F22" s="5">
-        <v>5531</v>
+        <v>5532</v>
       </c>
       <c r="G22" s="4">
         <f t="shared" si="1"/>
-        <v>0.90583033082214215</v>
+        <v>0.90599410415984283</v>
       </c>
       <c r="H22" s="5">
         <v>6184</v>
@@ -3654,14 +3654,14 @@
       </c>
       <c r="AI22" s="3">
         <f t="shared" si="11"/>
-        <v>4114</v>
+        <v>4115</v>
       </c>
       <c r="AJ22" s="5">
-        <v>6018</v>
+        <v>6019</v>
       </c>
       <c r="AK22" s="4">
         <f t="shared" si="12"/>
-        <v>0.91934005499541704</v>
+        <v>0.91949282004277422</v>
       </c>
       <c r="AL22" s="5">
         <v>6648</v>
@@ -3671,14 +3671,14 @@
       </c>
       <c r="AN22" s="3">
         <f t="shared" si="13"/>
-        <v>3820</v>
+        <v>3821</v>
       </c>
       <c r="AO22" s="5">
-        <v>6078</v>
+        <v>6079</v>
       </c>
       <c r="AP22" s="4">
         <f t="shared" si="14"/>
-        <v>0.91425992779783394</v>
+        <v>0.91441034897713602</v>
       </c>
       <c r="AQ22" s="3">
         <v>7880</v>
@@ -3688,14 +3688,14 @@
       </c>
       <c r="AS22" s="3">
         <f t="shared" si="15"/>
-        <v>4836</v>
+        <v>4837</v>
       </c>
       <c r="AT22" s="3">
-        <v>7292</v>
+        <v>7293</v>
       </c>
       <c r="AU22" s="4">
         <f t="shared" si="16"/>
-        <v>0.92538071065989846</v>
+        <v>0.92550761421319794</v>
       </c>
       <c r="AV22" s="5">
         <v>6715</v>
@@ -3705,14 +3705,14 @@
       </c>
       <c r="AX22" s="3">
         <f t="shared" si="17"/>
-        <v>3918</v>
+        <v>3919</v>
       </c>
       <c r="AY22" s="5">
-        <v>6101</v>
+        <v>6102</v>
       </c>
       <c r="AZ22" s="4">
         <f t="shared" si="18"/>
-        <v>0.90856291883842144</v>
+        <v>0.90871183916604614</v>
       </c>
       <c r="BA22" s="10">
         <v>6117</v>
@@ -3722,14 +3722,14 @@
       </c>
       <c r="BC22" s="3">
         <f t="shared" si="19"/>
-        <v>4031</v>
+        <v>4032</v>
       </c>
       <c r="BD22" s="5">
-        <v>6148</v>
+        <v>6149</v>
       </c>
       <c r="BE22" s="4">
         <f t="shared" si="20"/>
-        <v>1.0050678437142391</v>
+        <v>1.0052313225437306</v>
       </c>
       <c r="BF22" s="10">
         <v>7349</v>
@@ -3739,14 +3739,14 @@
       </c>
       <c r="BH22" s="3">
         <f t="shared" si="21"/>
-        <v>5148</v>
+        <v>5149</v>
       </c>
       <c r="BI22" s="5">
-        <v>7421</v>
+        <v>7422</v>
       </c>
       <c r="BJ22" s="4">
         <f t="shared" si="22"/>
-        <v>1.0097972513267111</v>
+        <v>1.0099333242618043</v>
       </c>
     </row>
     <row r="23" spans="1:62" x14ac:dyDescent="0.3">
@@ -3800,11 +3800,11 @@
         <v>9029</v>
       </c>
       <c r="P23" s="5">
-        <v>9125</v>
+        <v>9126</v>
       </c>
       <c r="Q23" s="4">
         <f t="shared" si="4"/>
-        <v>0.82363029154255796</v>
+        <v>0.82372055239642572</v>
       </c>
       <c r="R23" s="5">
         <v>9156</v>
@@ -3814,14 +3814,14 @@
       </c>
       <c r="T23" s="3">
         <f t="shared" si="5"/>
-        <v>5373</v>
+        <v>5374</v>
       </c>
       <c r="U23" s="5">
-        <v>7568</v>
+        <v>7569</v>
       </c>
       <c r="V23" s="4">
         <f t="shared" si="6"/>
-        <v>0.82656181738750545</v>
+        <v>0.82667103538663167</v>
       </c>
       <c r="W23" s="5">
         <v>9166</v>
@@ -3831,14 +3831,14 @@
       </c>
       <c r="Y23" s="3">
         <f t="shared" si="7"/>
-        <v>5710</v>
+        <v>5711</v>
       </c>
       <c r="Z23" s="5">
-        <v>7749</v>
+        <v>7750</v>
       </c>
       <c r="AA23" s="4">
         <f t="shared" si="8"/>
-        <v>0.84540693868644989</v>
+        <v>0.84551603753000215</v>
       </c>
       <c r="AB23" s="5">
         <v>11322</v>
@@ -3848,14 +3848,14 @@
       </c>
       <c r="AD23" s="3">
         <f t="shared" si="9"/>
-        <v>7306</v>
+        <v>7307</v>
       </c>
       <c r="AE23" s="5">
-        <v>10063</v>
+        <v>10064</v>
       </c>
       <c r="AF23" s="4">
         <f t="shared" si="10"/>
-        <v>0.88880056527115348</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="AG23" s="5">
         <v>9569</v>
@@ -3865,14 +3865,14 @@
       </c>
       <c r="AI23" s="3">
         <f t="shared" si="11"/>
-        <v>5889</v>
+        <v>5890</v>
       </c>
       <c r="AJ23" s="5">
-        <v>8235</v>
+        <v>8236</v>
       </c>
       <c r="AK23" s="4">
         <f t="shared" si="12"/>
-        <v>0.86059149336398788</v>
+        <v>0.86069599749190095</v>
       </c>
       <c r="AL23" s="5">
         <v>9502</v>
@@ -3882,14 +3882,14 @@
       </c>
       <c r="AN23" s="3">
         <f t="shared" si="13"/>
-        <v>6035</v>
+        <v>6036</v>
       </c>
       <c r="AO23" s="5">
-        <v>8361</v>
+        <v>8362</v>
       </c>
       <c r="AP23" s="4">
         <f t="shared" si="14"/>
-        <v>0.87992001683856025</v>
+        <v>0.8800252578404546</v>
       </c>
       <c r="AQ23" s="3">
         <v>11767</v>
@@ -3899,14 +3899,14 @@
       </c>
       <c r="AS23" s="3">
         <f t="shared" si="15"/>
-        <v>7341</v>
+        <v>7342</v>
       </c>
       <c r="AT23" s="3">
-        <v>10377</v>
+        <v>10378</v>
       </c>
       <c r="AU23" s="4">
         <f t="shared" si="16"/>
-        <v>0.8818730347582221</v>
+        <v>0.8819580181864537</v>
       </c>
       <c r="AV23" s="5">
         <v>9805</v>
@@ -3916,14 +3916,14 @@
       </c>
       <c r="AX23" s="3">
         <f t="shared" si="17"/>
-        <v>5856</v>
+        <v>5857</v>
       </c>
       <c r="AY23" s="5">
-        <v>8451</v>
+        <v>8452</v>
       </c>
       <c r="AZ23" s="4">
         <f t="shared" si="18"/>
-        <v>0.86190719020907702</v>
+        <v>0.86200917899031104</v>
       </c>
       <c r="BA23" s="10">
         <v>8694</v>
@@ -3933,14 +3933,14 @@
       </c>
       <c r="BC23" s="3">
         <f t="shared" si="19"/>
-        <v>6352</v>
+        <v>6353</v>
       </c>
       <c r="BD23" s="5">
-        <v>8559</v>
+        <v>8560</v>
       </c>
       <c r="BE23" s="4">
         <f t="shared" si="20"/>
-        <v>0.98447204968944102</v>
+        <v>0.98458707154359326</v>
       </c>
       <c r="BF23" s="10">
         <v>11229</v>
@@ -3950,14 +3950,14 @@
       </c>
       <c r="BH23" s="3">
         <f t="shared" si="21"/>
-        <v>7869</v>
+        <v>7870</v>
       </c>
       <c r="BI23" s="5">
-        <v>10638</v>
+        <v>10639</v>
       </c>
       <c r="BJ23" s="4">
         <f t="shared" si="22"/>
-        <v>0.94736842105263153</v>
+        <v>0.947457476177754</v>
       </c>
     </row>
     <row r="24" spans="1:62" x14ac:dyDescent="0.3">
@@ -4011,11 +4011,11 @@
         <v>5909</v>
       </c>
       <c r="P24" s="5">
-        <v>5945</v>
+        <v>5946</v>
       </c>
       <c r="Q24" s="4">
         <f t="shared" si="4"/>
-        <v>0.81977385548814119</v>
+        <v>0.81991174848317705</v>
       </c>
       <c r="R24" s="5">
         <v>6353</v>
@@ -4025,14 +4025,14 @@
       </c>
       <c r="T24" s="3">
         <f t="shared" si="5"/>
-        <v>3810</v>
+        <v>3811</v>
       </c>
       <c r="U24" s="5">
-        <v>5109</v>
+        <v>5110</v>
       </c>
       <c r="V24" s="4">
         <f t="shared" si="6"/>
-        <v>0.80418699826853457</v>
+        <v>0.80434440421847941</v>
       </c>
       <c r="W24" s="5">
         <v>6421</v>
@@ -4042,14 +4042,14 @@
       </c>
       <c r="Y24" s="3">
         <f t="shared" si="7"/>
-        <v>3899</v>
+        <v>3900</v>
       </c>
       <c r="Z24" s="5">
-        <v>5182</v>
+        <v>5183</v>
       </c>
       <c r="AA24" s="4">
         <f t="shared" si="8"/>
-        <v>0.80703940196231116</v>
+        <v>0.8071951409437782</v>
       </c>
       <c r="AB24" s="5">
         <v>7434</v>
@@ -4059,14 +4059,14 @@
       </c>
       <c r="AD24" s="3">
         <f t="shared" si="9"/>
-        <v>4719</v>
+        <v>4720</v>
       </c>
       <c r="AE24" s="5">
-        <v>6229</v>
+        <v>6230</v>
       </c>
       <c r="AF24" s="4">
         <f t="shared" si="10"/>
-        <v>0.83790691417810059</v>
+        <v>0.83804143126177022</v>
       </c>
       <c r="AG24" s="5">
         <v>6545</v>
@@ -4076,14 +4076,14 @@
       </c>
       <c r="AI24" s="3">
         <f t="shared" si="11"/>
-        <v>3945</v>
+        <v>3946</v>
       </c>
       <c r="AJ24" s="5">
-        <v>5346</v>
+        <v>5347</v>
       </c>
       <c r="AK24" s="4">
         <f t="shared" si="12"/>
-        <v>0.81680672268907561</v>
+        <v>0.81695951107715814</v>
       </c>
       <c r="AL24" s="5">
         <v>6623</v>
@@ -4093,14 +4093,14 @@
       </c>
       <c r="AN24" s="3">
         <f t="shared" si="13"/>
-        <v>4059</v>
+        <v>4060</v>
       </c>
       <c r="AO24" s="5">
-        <v>5431</v>
+        <v>5432</v>
       </c>
       <c r="AP24" s="4">
         <f t="shared" si="14"/>
-        <v>0.82002113845689262</v>
+        <v>0.82017212743469725</v>
       </c>
       <c r="AQ24" s="3">
         <v>7610</v>
@@ -4110,14 +4110,14 @@
       </c>
       <c r="AS24" s="3">
         <f t="shared" si="15"/>
-        <v>4917</v>
+        <v>4918</v>
       </c>
       <c r="AT24" s="3">
-        <v>6400</v>
+        <v>6401</v>
       </c>
       <c r="AU24" s="4">
         <f t="shared" si="16"/>
-        <v>0.84099868593955318</v>
+        <v>0.84113009198423128</v>
       </c>
       <c r="AV24" s="5">
         <v>6365</v>
@@ -4127,14 +4127,14 @@
       </c>
       <c r="AX24" s="3">
         <f t="shared" si="17"/>
-        <v>4032</v>
+        <v>4033</v>
       </c>
       <c r="AY24" s="5">
-        <v>5442</v>
+        <v>5443</v>
       </c>
       <c r="AZ24" s="4">
         <f t="shared" si="18"/>
-        <v>0.85498821681068338</v>
+        <v>0.85514532600157112</v>
       </c>
       <c r="BA24" s="10">
         <v>5683</v>
@@ -4144,14 +4144,14 @@
       </c>
       <c r="BC24" s="3">
         <f t="shared" si="19"/>
-        <v>4122</v>
+        <v>4123</v>
       </c>
       <c r="BD24" s="5">
-        <v>5486</v>
+        <v>5487</v>
       </c>
       <c r="BE24" s="4">
         <f t="shared" si="20"/>
-        <v>0.96533521027626257</v>
+        <v>0.96551117367587547</v>
       </c>
       <c r="BF24" s="10">
         <v>6688</v>
@@ -4161,14 +4161,14 @@
       </c>
       <c r="BH24" s="3">
         <f t="shared" si="21"/>
-        <v>5039</v>
+        <v>5040</v>
       </c>
       <c r="BI24" s="5">
-        <v>6507</v>
+        <v>6508</v>
       </c>
       <c r="BJ24" s="4">
         <f t="shared" si="22"/>
-        <v>0.97293660287081341</v>
+        <v>0.97308612440191389</v>
       </c>
     </row>
     <row r="25" spans="1:62" x14ac:dyDescent="0.3">
@@ -4186,14 +4186,14 @@
       </c>
       <c r="E25" s="3">
         <f t="shared" si="0"/>
-        <v>9249</v>
+        <v>9250</v>
       </c>
       <c r="F25" s="5">
-        <v>17191</v>
+        <v>17192</v>
       </c>
       <c r="G25" s="4">
         <f t="shared" si="1"/>
-        <v>0.90588607261421716</v>
+        <v>0.90593876798229434</v>
       </c>
       <c r="H25" s="5">
         <v>19277</v>
@@ -4203,14 +4203,14 @@
       </c>
       <c r="J25" s="3">
         <f t="shared" si="2"/>
-        <v>8613</v>
+        <v>8614</v>
       </c>
       <c r="K25" s="5">
-        <v>17432</v>
+        <v>17433</v>
       </c>
       <c r="L25" s="4">
         <f t="shared" si="3"/>
-        <v>0.90429008663173727</v>
+        <v>0.90434196192353578</v>
       </c>
       <c r="M25" s="9">
         <v>26614</v>
@@ -4222,11 +4222,11 @@
         <v>24298</v>
       </c>
       <c r="P25" s="5">
-        <v>24429</v>
+        <v>24430</v>
       </c>
       <c r="Q25" s="4">
         <f t="shared" si="4"/>
-        <v>0.91790035319756524</v>
+        <v>0.91793792740662805</v>
       </c>
       <c r="R25" s="5">
         <v>19402</v>
@@ -4236,14 +4236,14 @@
       </c>
       <c r="T25" s="3">
         <f t="shared" si="5"/>
-        <v>9099</v>
+        <v>9100</v>
       </c>
       <c r="U25" s="5">
-        <v>17573</v>
+        <v>17574</v>
       </c>
       <c r="V25" s="4">
         <f t="shared" si="6"/>
-        <v>0.90573136790021647</v>
+        <v>0.90578290897845581</v>
       </c>
       <c r="W25" s="5">
         <v>19474</v>
@@ -4253,14 +4253,14 @@
       </c>
       <c r="Y25" s="3">
         <f t="shared" si="7"/>
-        <v>9547</v>
+        <v>9548</v>
       </c>
       <c r="Z25" s="5">
-        <v>17815</v>
+        <v>17816</v>
       </c>
       <c r="AA25" s="4">
         <f t="shared" si="8"/>
-        <v>0.91480948957584474</v>
+        <v>0.91486084009448498</v>
       </c>
       <c r="AB25" s="5">
         <v>27081</v>
@@ -4270,14 +4270,14 @@
       </c>
       <c r="AD25" s="3">
         <f t="shared" si="9"/>
-        <v>15025</v>
+        <v>15026</v>
       </c>
       <c r="AE25" s="5">
-        <v>25204</v>
+        <v>25205</v>
       </c>
       <c r="AF25" s="4">
         <f t="shared" si="10"/>
-        <v>0.93068941324175625</v>
+        <v>0.93072633950001848</v>
       </c>
       <c r="AG25" s="5">
         <v>19543</v>
@@ -4287,14 +4287,14 @@
       </c>
       <c r="AI25" s="3">
         <f t="shared" si="11"/>
-        <v>8974</v>
+        <v>8975</v>
       </c>
       <c r="AJ25" s="5">
-        <v>18101</v>
+        <v>18102</v>
       </c>
       <c r="AK25" s="4">
         <f t="shared" si="12"/>
-        <v>0.92621398966381829</v>
+        <v>0.92626515888041749</v>
       </c>
       <c r="AL25" s="5">
         <v>19594</v>
@@ -4304,14 +4304,14 @@
       </c>
       <c r="AN25" s="3">
         <f t="shared" si="13"/>
-        <v>9106</v>
+        <v>9107</v>
       </c>
       <c r="AO25" s="5">
-        <v>18274</v>
+        <v>18275</v>
       </c>
       <c r="AP25" s="4">
         <f t="shared" si="14"/>
-        <v>0.93263243850158206</v>
+        <v>0.93268347453302036</v>
       </c>
       <c r="AQ25" s="3">
         <v>26830</v>
@@ -4321,14 +4321,14 @@
       </c>
       <c r="AS25" s="3">
         <f t="shared" si="15"/>
-        <v>13143</v>
+        <v>13144</v>
       </c>
       <c r="AT25" s="3">
-        <v>25473</v>
+        <v>25474</v>
       </c>
       <c r="AU25" s="4">
         <f t="shared" si="16"/>
-        <v>0.94942228848304133</v>
+        <v>0.94945956019381295</v>
       </c>
       <c r="AV25" s="5">
         <v>19719</v>
@@ -4338,14 +4338,14 @@
       </c>
       <c r="AX25" s="3">
         <f t="shared" si="17"/>
-        <v>8712</v>
+        <v>8713</v>
       </c>
       <c r="AY25" s="5">
-        <v>18367</v>
+        <v>18368</v>
       </c>
       <c r="AZ25" s="4">
         <f t="shared" si="18"/>
-        <v>0.93143668543029567</v>
+        <v>0.93148739794107205</v>
       </c>
       <c r="BA25" s="10">
         <v>18241</v>
@@ -4355,14 +4355,14 @@
       </c>
       <c r="BC25" s="3">
         <f t="shared" si="19"/>
-        <v>9438</v>
+        <v>9439</v>
       </c>
       <c r="BD25" s="5">
-        <v>18419</v>
+        <v>18420</v>
       </c>
       <c r="BE25" s="4">
         <f t="shared" si="20"/>
-        <v>1.0097582369387643</v>
+        <v>1.0098130584946001</v>
       </c>
       <c r="BF25" s="10">
         <v>25358</v>
@@ -4372,14 +4372,14 @@
       </c>
       <c r="BH25" s="3">
         <f t="shared" si="21"/>
-        <v>15168</v>
+        <v>15169</v>
       </c>
       <c r="BI25" s="5">
-        <v>25702</v>
+        <v>25703</v>
       </c>
       <c r="BJ25" s="4">
         <f t="shared" si="22"/>
-        <v>1.0135657386229198</v>
+        <v>1.0136051739096144</v>
       </c>
     </row>
     <row r="26" spans="1:62" x14ac:dyDescent="0.3">
@@ -4397,14 +4397,14 @@
       </c>
       <c r="E26" s="3">
         <f t="shared" si="0"/>
-        <v>7692</v>
+        <v>7697</v>
       </c>
       <c r="F26" s="5">
-        <v>11666</v>
+        <v>11671</v>
       </c>
       <c r="G26" s="4">
         <f t="shared" si="1"/>
-        <v>0.72876061969015493</v>
+        <v>0.72907296351824091</v>
       </c>
       <c r="H26" s="5">
         <v>16365</v>
@@ -4414,14 +4414,14 @@
       </c>
       <c r="J26" s="3">
         <f t="shared" si="2"/>
-        <v>7793</v>
+        <v>7799</v>
       </c>
       <c r="K26" s="5">
-        <v>12091</v>
+        <v>12097</v>
       </c>
       <c r="L26" s="4">
         <f t="shared" si="3"/>
-        <v>0.73883287503819128</v>
+        <v>0.73919951115184845</v>
       </c>
       <c r="M26" s="9">
         <v>27510</v>
@@ -4433,11 +4433,11 @@
         <v>21793</v>
       </c>
       <c r="P26" s="5">
-        <v>22093</v>
+        <v>22101</v>
       </c>
       <c r="Q26" s="4">
         <f t="shared" si="4"/>
-        <v>0.80308978553253363</v>
+        <v>0.80338058887677211</v>
       </c>
       <c r="R26" s="5">
         <v>16566</v>
@@ -4447,14 +4447,14 @@
       </c>
       <c r="T26" s="3">
         <f t="shared" si="5"/>
-        <v>7994</v>
+        <v>8000</v>
       </c>
       <c r="U26" s="5">
-        <v>12452</v>
+        <v>12458</v>
       </c>
       <c r="V26" s="4">
         <f t="shared" si="6"/>
-        <v>0.75166002656042497</v>
+        <v>0.75202221417360859</v>
       </c>
       <c r="W26" s="5">
         <v>16728</v>
@@ -4464,14 +4464,14 @@
       </c>
       <c r="Y26" s="3">
         <f t="shared" si="7"/>
-        <v>8690</v>
+        <v>8695</v>
       </c>
       <c r="Z26" s="5">
-        <v>12689</v>
+        <v>12694</v>
       </c>
       <c r="AA26" s="4">
         <f t="shared" si="8"/>
-        <v>0.75854854136776662</v>
+        <v>0.75884744141559057</v>
       </c>
       <c r="AB26" s="5">
         <v>28240</v>
@@ -4481,14 +4481,14 @@
       </c>
       <c r="AD26" s="3">
         <f t="shared" si="9"/>
-        <v>18097</v>
+        <v>18102</v>
       </c>
       <c r="AE26" s="5">
-        <v>24963</v>
+        <v>24968</v>
       </c>
       <c r="AF26" s="4">
         <f t="shared" si="10"/>
-        <v>0.88395892351274785</v>
+        <v>0.88413597733711047</v>
       </c>
       <c r="AG26" s="5">
         <v>16538</v>
@@ -4498,14 +4498,14 @@
       </c>
       <c r="AI26" s="3">
         <f t="shared" si="11"/>
-        <v>8858</v>
+        <v>8861</v>
       </c>
       <c r="AJ26" s="5">
-        <v>13475</v>
+        <v>13478</v>
       </c>
       <c r="AK26" s="4">
         <f t="shared" si="12"/>
-        <v>0.81479018019107508</v>
+        <v>0.81497158060224939</v>
       </c>
       <c r="AL26" s="5">
         <v>16671</v>
@@ -4515,14 +4515,14 @@
       </c>
       <c r="AN26" s="3">
         <f t="shared" si="13"/>
-        <v>8885</v>
+        <v>8888</v>
       </c>
       <c r="AO26" s="5">
-        <v>13579</v>
+        <v>13582</v>
       </c>
       <c r="AP26" s="4">
         <f t="shared" si="14"/>
-        <v>0.81452822266210789</v>
+        <v>0.81470817587427269</v>
       </c>
       <c r="AQ26" s="3">
         <v>28406</v>
@@ -4532,14 +4532,14 @@
       </c>
       <c r="AS26" s="3">
         <f t="shared" si="15"/>
-        <v>17043</v>
+        <v>17048</v>
       </c>
       <c r="AT26" s="3">
-        <v>25117</v>
+        <v>25122</v>
       </c>
       <c r="AU26" s="4">
         <f t="shared" si="16"/>
-        <v>0.88421460254875728</v>
+        <v>0.88439062169964089</v>
       </c>
       <c r="AV26" s="5">
         <v>16717</v>
@@ -4549,14 +4549,14 @@
       </c>
       <c r="AX26" s="3">
         <f t="shared" si="17"/>
-        <v>8249</v>
+        <v>8252</v>
       </c>
       <c r="AY26" s="5">
-        <v>13279</v>
+        <v>13282</v>
       </c>
       <c r="AZ26" s="4">
         <f t="shared" si="18"/>
-        <v>0.79434108990847641</v>
+        <v>0.79452054794520544</v>
       </c>
       <c r="BA26" s="10">
         <v>13719</v>
@@ -4566,14 +4566,14 @@
       </c>
       <c r="BC26" s="3">
         <f t="shared" si="19"/>
-        <v>8542</v>
+        <v>8545</v>
       </c>
       <c r="BD26" s="5">
-        <v>13376</v>
+        <v>13379</v>
       </c>
       <c r="BE26" s="4">
         <f t="shared" si="20"/>
-        <v>0.97499817770974562</v>
+        <v>0.97521685254027257</v>
       </c>
       <c r="BF26" s="10">
         <v>25779</v>
@@ -4583,14 +4583,14 @@
       </c>
       <c r="BH26" s="3">
         <f t="shared" si="21"/>
-        <v>17879</v>
+        <v>17885</v>
       </c>
       <c r="BI26" s="5">
-        <v>25164</v>
+        <v>25170</v>
       </c>
       <c r="BJ26" s="4">
         <f t="shared" si="22"/>
-        <v>0.97614337251251015</v>
+        <v>0.97637612009775399</v>
       </c>
     </row>
     <row r="27" spans="1:62" x14ac:dyDescent="0.3">
@@ -4608,14 +4608,14 @@
       </c>
       <c r="E27" s="3">
         <f t="shared" si="0"/>
-        <v>70252</v>
+        <v>70256</v>
       </c>
       <c r="F27" s="5">
-        <v>109142</v>
+        <v>109146</v>
       </c>
       <c r="G27" s="4">
         <f t="shared" si="1"/>
-        <v>0.92098290381921588</v>
+        <v>0.92101665738443628</v>
       </c>
       <c r="H27" s="5">
         <v>121212</v>
@@ -4625,14 +4625,14 @@
       </c>
       <c r="J27" s="3">
         <f t="shared" si="2"/>
-        <v>66320</v>
+        <v>66324</v>
       </c>
       <c r="K27" s="5">
-        <v>111217</v>
+        <v>111221</v>
       </c>
       <c r="L27" s="4">
         <f t="shared" si="3"/>
-        <v>0.91754116754116755</v>
+        <v>0.91757416757416754</v>
       </c>
       <c r="M27" s="9">
         <v>178312</v>
@@ -4644,11 +4644,11 @@
         <v>161829</v>
       </c>
       <c r="P27" s="5">
-        <v>163129</v>
+        <v>163136</v>
       </c>
       <c r="Q27" s="4">
         <f t="shared" si="4"/>
-        <v>0.9148514962537575</v>
+        <v>0.91489075328637448</v>
       </c>
       <c r="R27" s="5">
         <v>121489</v>
@@ -4658,14 +4658,14 @@
       </c>
       <c r="T27" s="3">
         <f t="shared" si="5"/>
-        <v>67709</v>
+        <v>67716</v>
       </c>
       <c r="U27" s="5">
-        <v>111737</v>
+        <v>111744</v>
       </c>
       <c r="V27" s="4">
         <f t="shared" si="6"/>
-        <v>0.91972935821350077</v>
+        <v>0.91978697659870445</v>
       </c>
       <c r="W27" s="5">
         <v>123451</v>
@@ -4675,14 +4675,14 @@
       </c>
       <c r="Y27" s="3">
         <f t="shared" si="7"/>
-        <v>70993</v>
+        <v>71000</v>
       </c>
       <c r="Z27" s="5">
-        <v>113719</v>
+        <v>113726</v>
       </c>
       <c r="AA27" s="4">
         <f t="shared" si="8"/>
-        <v>0.92116710273711833</v>
+        <v>0.92122380539647308</v>
       </c>
       <c r="AB27" s="5">
         <v>182601</v>
@@ -4692,14 +4692,14 @@
       </c>
       <c r="AD27" s="3">
         <f t="shared" si="9"/>
-        <v>117983</v>
+        <v>117990</v>
       </c>
       <c r="AE27" s="5">
-        <v>173255</v>
+        <v>173262</v>
       </c>
       <c r="AF27" s="4">
         <f t="shared" si="10"/>
-        <v>0.94881736682712581</v>
+        <v>0.94885570177600342</v>
       </c>
       <c r="AG27" s="5">
         <v>124689</v>
@@ -4709,14 +4709,14 @@
       </c>
       <c r="AI27" s="3">
         <f t="shared" si="11"/>
-        <v>69025</v>
+        <v>69032</v>
       </c>
       <c r="AJ27" s="5">
-        <v>117356</v>
+        <v>117363</v>
       </c>
       <c r="AK27" s="4">
         <f t="shared" si="12"/>
-        <v>0.94118967992364999</v>
+        <v>0.94124581959916276</v>
       </c>
       <c r="AL27" s="5">
         <v>127177</v>
@@ -4726,14 +4726,14 @@
       </c>
       <c r="AN27" s="3">
         <f t="shared" si="13"/>
-        <v>69464</v>
+        <v>69471</v>
       </c>
       <c r="AO27" s="5">
-        <v>119051</v>
+        <v>119058</v>
       </c>
       <c r="AP27" s="4">
         <f t="shared" si="14"/>
-        <v>0.93610479882368669</v>
+        <v>0.93615984022268173</v>
       </c>
       <c r="AQ27" s="3">
         <v>185152</v>
@@ -4743,14 +4743,14 @@
       </c>
       <c r="AS27" s="3">
         <f t="shared" si="15"/>
-        <v>105627</v>
+        <v>105637</v>
       </c>
       <c r="AT27" s="3">
-        <v>176823</v>
+        <v>176833</v>
       </c>
       <c r="AU27" s="4">
         <f t="shared" si="16"/>
-        <v>0.95501533874870381</v>
+        <v>0.95506934842723812</v>
       </c>
       <c r="AV27" s="5">
         <v>127611</v>
@@ -4760,14 +4760,14 @@
       </c>
       <c r="AX27" s="3">
         <f t="shared" si="17"/>
-        <v>66572</v>
+        <v>66581</v>
       </c>
       <c r="AY27" s="5">
-        <v>119119</v>
+        <v>119128</v>
       </c>
       <c r="AZ27" s="4">
         <f t="shared" si="18"/>
-        <v>0.93345401258512195</v>
+        <v>0.93352453942058289</v>
       </c>
       <c r="BA27" s="10">
         <v>122070</v>
@@ -4777,14 +4777,14 @@
       </c>
       <c r="BC27" s="3">
         <f t="shared" si="19"/>
-        <v>69516</v>
+        <v>69525</v>
       </c>
       <c r="BD27" s="5">
-        <v>120781</v>
+        <v>120790</v>
       </c>
       <c r="BE27" s="4">
         <f t="shared" si="20"/>
-        <v>0.98944048496764148</v>
+        <v>0.98951421315638566</v>
       </c>
       <c r="BF27" s="10">
         <v>180737</v>
@@ -4794,14 +4794,14 @@
       </c>
       <c r="BH27" s="3">
         <f t="shared" si="21"/>
-        <v>116083</v>
+        <v>116094</v>
       </c>
       <c r="BI27" s="5">
-        <v>179748</v>
+        <v>179759</v>
       </c>
       <c r="BJ27" s="4">
         <f t="shared" si="22"/>
-        <v>0.99452796051721559</v>
+        <v>0.99458882243259539</v>
       </c>
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.3">
@@ -4855,11 +4855,11 @@
         <v>594498</v>
       </c>
       <c r="P28" s="5">
-        <v>595748</v>
+        <v>595749</v>
       </c>
       <c r="Q28" s="4">
         <f t="shared" si="4"/>
-        <v>0.94028851920830836</v>
+        <v>0.94029009754095771</v>
       </c>
       <c r="R28" s="5">
         <v>370844</v>
@@ -4903,14 +4903,14 @@
       </c>
       <c r="AD28" s="3">
         <f t="shared" si="9"/>
-        <v>319761</v>
+        <v>319762</v>
       </c>
       <c r="AE28" s="5">
-        <v>621208</v>
+        <v>621209</v>
       </c>
       <c r="AF28" s="4">
         <f t="shared" si="10"/>
-        <v>0.96587453121793154</v>
+        <v>0.96587608605066266</v>
       </c>
       <c r="AG28" s="5">
         <v>378725</v>
@@ -4954,14 +4954,14 @@
       </c>
       <c r="AS28" s="3">
         <f t="shared" si="15"/>
-        <v>268774</v>
+        <v>268775</v>
       </c>
       <c r="AT28" s="3">
-        <v>629791</v>
+        <v>629792</v>
       </c>
       <c r="AU28" s="4">
         <f t="shared" si="16"/>
-        <v>0.96440914930792165</v>
+        <v>0.96441068062410318</v>
       </c>
       <c r="AV28" s="5">
         <v>393378</v>
@@ -5005,14 +5005,14 @@
       </c>
       <c r="BH28" s="3">
         <f t="shared" si="21"/>
-        <v>301327</v>
+        <v>301328</v>
       </c>
       <c r="BI28" s="5">
-        <v>640676</v>
+        <v>640677</v>
       </c>
       <c r="BJ28" s="4">
         <f t="shared" si="22"/>
-        <v>0.99558983953729052</v>
+        <v>0.99559139350503645</v>
       </c>
     </row>
     <row r="29" spans="1:62" x14ac:dyDescent="0.3">
@@ -5030,14 +5030,14 @@
       </c>
       <c r="E29" s="3">
         <f t="shared" si="0"/>
-        <v>61358</v>
+        <v>61359</v>
       </c>
       <c r="F29" s="5">
-        <v>113610</v>
+        <v>113611</v>
       </c>
       <c r="G29" s="4">
         <f t="shared" si="1"/>
-        <v>0.94236798885183892</v>
+        <v>0.94237628361452574</v>
       </c>
       <c r="H29" s="5">
         <v>121339</v>
@@ -5047,14 +5047,14 @@
       </c>
       <c r="J29" s="3">
         <f t="shared" si="2"/>
-        <v>63075</v>
+        <v>63076</v>
       </c>
       <c r="K29" s="5">
-        <v>114673</v>
+        <v>114674</v>
       </c>
       <c r="L29" s="4">
         <f t="shared" si="3"/>
-        <v>0.94506300529920306</v>
+        <v>0.9450712466725455</v>
       </c>
       <c r="M29" s="9">
         <v>168897</v>
@@ -5066,11 +5066,11 @@
         <v>159082</v>
       </c>
       <c r="P29" s="5">
-        <v>159524</v>
+        <v>159527</v>
       </c>
       <c r="Q29" s="4">
         <f t="shared" si="4"/>
-        <v>0.94450463892194647</v>
+        <v>0.94452240122678321</v>
       </c>
       <c r="R29" s="5">
         <v>122532</v>
@@ -5114,14 +5114,14 @@
       </c>
       <c r="AD29" s="3">
         <f t="shared" si="9"/>
-        <v>96106</v>
+        <v>96108</v>
       </c>
       <c r="AE29" s="5">
-        <v>166284</v>
+        <v>166286</v>
       </c>
       <c r="AF29" s="4">
         <f t="shared" si="10"/>
-        <v>0.96299942666195637</v>
+        <v>0.96301100924869554</v>
       </c>
       <c r="AG29" s="5">
         <v>125793</v>
@@ -5165,14 +5165,14 @@
       </c>
       <c r="AS29" s="3">
         <f t="shared" si="15"/>
-        <v>84975</v>
+        <v>84977</v>
       </c>
       <c r="AT29" s="3">
-        <v>169375</v>
+        <v>169377</v>
       </c>
       <c r="AU29" s="4">
         <f t="shared" si="16"/>
-        <v>0.96326648998487208</v>
+        <v>0.96327786434932949</v>
       </c>
       <c r="AV29" s="5">
         <v>130198</v>
@@ -5199,14 +5199,14 @@
       </c>
       <c r="BC29" s="3">
         <f t="shared" si="19"/>
-        <v>63486</v>
+        <v>63487</v>
       </c>
       <c r="BD29" s="5">
-        <v>125567</v>
+        <v>125568</v>
       </c>
       <c r="BE29" s="4">
         <f t="shared" si="20"/>
-        <v>0.9844917480105061</v>
+        <v>0.98449958838057161</v>
       </c>
       <c r="BF29" s="10">
         <v>174166</v>
@@ -5216,14 +5216,14 @@
       </c>
       <c r="BH29" s="3">
         <f t="shared" si="21"/>
-        <v>93441</v>
+        <v>93444</v>
       </c>
       <c r="BI29" s="5">
-        <v>172944</v>
+        <v>172947</v>
       </c>
       <c r="BJ29" s="4">
         <f t="shared" si="22"/>
-        <v>0.99298370520078549</v>
+        <v>0.993000930147101</v>
       </c>
     </row>
     <row r="30" spans="1:62" x14ac:dyDescent="0.3">
@@ -5488,11 +5488,11 @@
         <v>124102</v>
       </c>
       <c r="P31" s="5">
-        <v>124759</v>
+        <v>124762</v>
       </c>
       <c r="Q31" s="4">
         <f t="shared" si="4"/>
-        <v>0.94404969996897536</v>
+        <v>0.94407240092922595</v>
       </c>
       <c r="R31" s="5">
         <v>74474</v>
@@ -5519,14 +5519,14 @@
       </c>
       <c r="Y31" s="3">
         <f t="shared" si="7"/>
-        <v>36679</v>
+        <v>36680</v>
       </c>
       <c r="Z31" s="5">
-        <v>71283</v>
+        <v>71284</v>
       </c>
       <c r="AA31" s="4">
         <f t="shared" si="8"/>
-        <v>0.94168857418391749</v>
+        <v>0.94170178474708377</v>
       </c>
       <c r="AB31" s="5">
         <v>133809</v>
@@ -5536,14 +5536,14 @@
       </c>
       <c r="AD31" s="3">
         <f t="shared" si="9"/>
-        <v>73413</v>
+        <v>73415</v>
       </c>
       <c r="AE31" s="5">
-        <v>129299</v>
+        <v>129301</v>
       </c>
       <c r="AF31" s="4">
         <f t="shared" si="10"/>
-        <v>0.96629524172514558</v>
+        <v>0.96631018840287275</v>
       </c>
       <c r="AG31" s="5">
         <v>75434</v>
@@ -5587,14 +5587,14 @@
       </c>
       <c r="AS31" s="3">
         <f t="shared" si="15"/>
-        <v>64957</v>
+        <v>64959</v>
       </c>
       <c r="AT31" s="3">
-        <v>131249</v>
+        <v>131251</v>
       </c>
       <c r="AU31" s="4">
         <f t="shared" si="16"/>
-        <v>0.9682985849822201</v>
+        <v>0.96831334012069703</v>
       </c>
       <c r="AV31" s="5">
         <v>78435</v>
@@ -5604,14 +5604,14 @@
       </c>
       <c r="AX31" s="3">
         <f t="shared" si="17"/>
-        <v>30762</v>
+        <v>30763</v>
       </c>
       <c r="AY31" s="5">
-        <v>73086</v>
+        <v>73087</v>
       </c>
       <c r="AZ31" s="4">
         <f t="shared" si="18"/>
-        <v>0.93180340409256068</v>
+        <v>0.93181615350290048</v>
       </c>
       <c r="BA31" s="10">
         <v>76166</v>
@@ -5621,14 +5621,14 @@
       </c>
       <c r="BC31" s="3">
         <f t="shared" si="19"/>
-        <v>33776</v>
+        <v>33777</v>
       </c>
       <c r="BD31" s="5">
-        <v>74313</v>
+        <v>74314</v>
       </c>
       <c r="BE31" s="4">
         <f t="shared" si="20"/>
-        <v>0.97567155948848572</v>
+        <v>0.97568468870624692</v>
       </c>
       <c r="BF31" s="10">
         <v>132970</v>
@@ -5638,14 +5638,14 @@
       </c>
       <c r="BH31" s="3">
         <f t="shared" si="21"/>
-        <v>74230</v>
+        <v>74231</v>
       </c>
       <c r="BI31" s="5">
-        <v>133205</v>
+        <v>133206</v>
       </c>
       <c r="BJ31" s="4">
         <f t="shared" si="22"/>
-        <v>1.0017673159359255</v>
+        <v>1.0017748364292698</v>
       </c>
     </row>
     <row r="32" spans="1:62" x14ac:dyDescent="0.3">
@@ -5663,14 +5663,14 @@
       </c>
       <c r="E32" s="3">
         <f t="shared" si="0"/>
-        <v>91612</v>
+        <v>91615</v>
       </c>
       <c r="F32" s="5">
-        <v>184446</v>
+        <v>184449</v>
       </c>
       <c r="G32" s="4">
         <f t="shared" si="1"/>
-        <v>0.96066625694017649</v>
+        <v>0.96068188210293859</v>
       </c>
       <c r="H32" s="5">
         <v>196288</v>
@@ -5680,14 +5680,14 @@
       </c>
       <c r="J32" s="3">
         <f t="shared" si="2"/>
-        <v>87698</v>
+        <v>87700</v>
       </c>
       <c r="K32" s="5">
-        <v>188231</v>
+        <v>188233</v>
       </c>
       <c r="L32" s="4">
         <f t="shared" si="3"/>
-        <v>0.95895317085099441</v>
+        <v>0.95896335996087378</v>
       </c>
       <c r="M32" s="9">
         <v>418497</v>
@@ -5699,11 +5699,11 @@
         <v>397306</v>
       </c>
       <c r="P32" s="5">
-        <v>398332</v>
+        <v>398333</v>
       </c>
       <c r="Q32" s="4">
         <f t="shared" si="4"/>
-        <v>0.95181566415051955</v>
+        <v>0.95181805365390915</v>
       </c>
       <c r="R32" s="5">
         <v>194320</v>
@@ -5713,14 +5713,14 @@
       </c>
       <c r="T32" s="3">
         <f t="shared" si="5"/>
-        <v>94019</v>
+        <v>94021</v>
       </c>
       <c r="U32" s="5">
-        <v>186168</v>
+        <v>186170</v>
       </c>
       <c r="V32" s="4">
         <f t="shared" si="6"/>
-        <v>0.95804857966241252</v>
+        <v>0.95805887196377115</v>
       </c>
       <c r="W32" s="5">
         <v>198209</v>
@@ -5730,14 +5730,14 @@
       </c>
       <c r="Y32" s="3">
         <f t="shared" si="7"/>
-        <v>97020</v>
+        <v>97022</v>
       </c>
       <c r="Z32" s="5">
-        <v>190200</v>
+        <v>190202</v>
       </c>
       <c r="AA32" s="4">
         <f t="shared" si="8"/>
-        <v>0.95959315671841339</v>
+        <v>0.95960324707757971</v>
       </c>
       <c r="AB32" s="5">
         <v>426405</v>
@@ -5747,14 +5747,14 @@
       </c>
       <c r="AD32" s="3">
         <f t="shared" si="9"/>
-        <v>243327</v>
+        <v>243328</v>
       </c>
       <c r="AE32" s="5">
-        <v>418626</v>
+        <v>418627</v>
       </c>
       <c r="AF32" s="4">
         <f t="shared" si="10"/>
-        <v>0.9817567805255567</v>
+        <v>0.98175912571381663</v>
       </c>
       <c r="AG32" s="5">
         <v>199136</v>
@@ -5764,14 +5764,14 @@
       </c>
       <c r="AI32" s="3">
         <f t="shared" si="11"/>
-        <v>82208</v>
+        <v>82210</v>
       </c>
       <c r="AJ32" s="5">
-        <v>194598</v>
+        <v>194600</v>
       </c>
       <c r="AK32" s="4">
         <f t="shared" si="12"/>
-        <v>0.97721155391290371</v>
+        <v>0.97722159730033742</v>
       </c>
       <c r="AL32" s="5">
         <v>204506</v>
@@ -5781,14 +5781,14 @@
       </c>
       <c r="AN32" s="3">
         <f t="shared" si="13"/>
-        <v>84512</v>
+        <v>84514</v>
       </c>
       <c r="AO32" s="5">
-        <v>199094</v>
+        <v>199096</v>
       </c>
       <c r="AP32" s="4">
         <f t="shared" si="14"/>
-        <v>0.97353622876590418</v>
+        <v>0.97354600843007055</v>
       </c>
       <c r="AQ32" s="3">
         <v>435626</v>
@@ -5798,14 +5798,14 @@
       </c>
       <c r="AS32" s="3">
         <f t="shared" si="15"/>
-        <v>206042</v>
+        <v>206044</v>
       </c>
       <c r="AT32" s="3">
-        <v>427434</v>
+        <v>427436</v>
       </c>
       <c r="AU32" s="4">
         <f t="shared" si="16"/>
-        <v>0.98119487817531548</v>
+        <v>0.98119946926951096</v>
       </c>
       <c r="AV32" s="5">
         <v>208760</v>
@@ -5815,14 +5815,14 @@
       </c>
       <c r="AX32" s="3">
         <f t="shared" si="17"/>
-        <v>78092</v>
+        <v>78094</v>
       </c>
       <c r="AY32" s="5">
-        <v>198451</v>
+        <v>198453</v>
       </c>
       <c r="AZ32" s="4">
         <f t="shared" si="18"/>
-        <v>0.95061793447020504</v>
+        <v>0.95062751484958807</v>
       </c>
       <c r="BA32" s="10">
         <v>206539</v>
@@ -5832,14 +5832,14 @@
       </c>
       <c r="BC32" s="3">
         <f t="shared" si="19"/>
-        <v>86629</v>
+        <v>86631</v>
       </c>
       <c r="BD32" s="5">
-        <v>203326</v>
+        <v>203328</v>
       </c>
       <c r="BE32" s="4">
         <f t="shared" si="20"/>
-        <v>0.98444361597567531</v>
+        <v>0.98445329937687309</v>
       </c>
       <c r="BF32" s="10">
         <v>435831</v>
@@ -5849,14 +5849,14 @@
       </c>
       <c r="BH32" s="3">
         <f t="shared" si="21"/>
-        <v>241657</v>
+        <v>241659</v>
       </c>
       <c r="BI32" s="5">
-        <v>436078</v>
+        <v>436080</v>
       </c>
       <c r="BJ32" s="4">
         <f t="shared" si="22"/>
-        <v>1.0005667334356665</v>
+        <v>1.0005713223703683</v>
       </c>
     </row>
     <row r="33" spans="1:62" x14ac:dyDescent="0.3">
@@ -5874,14 +5874,14 @@
       </c>
       <c r="E33" s="3">
         <f t="shared" si="0"/>
-        <v>112237</v>
+        <v>112238</v>
       </c>
       <c r="F33" s="5">
-        <v>577927</v>
+        <v>577928</v>
       </c>
       <c r="G33" s="4">
         <f t="shared" si="1"/>
-        <v>0.98537101858971843</v>
+        <v>0.9853727235992068</v>
       </c>
       <c r="H33" s="5">
         <v>594451</v>
@@ -6043,14 +6043,14 @@
       </c>
       <c r="BC33" s="3">
         <f t="shared" si="19"/>
-        <v>85343</v>
+        <v>85344</v>
       </c>
       <c r="BD33" s="5">
-        <v>616848</v>
+        <v>616849</v>
       </c>
       <c r="BE33" s="4">
         <f t="shared" si="20"/>
-        <v>0.99969045716721305</v>
+        <v>0.99969207781031666</v>
       </c>
       <c r="BF33" s="10">
         <v>1025594</v>
@@ -6060,14 +6060,14 @@
       </c>
       <c r="BH33" s="3">
         <f t="shared" si="21"/>
-        <v>198103</v>
+        <v>198104</v>
       </c>
       <c r="BI33" s="5">
-        <v>1029964</v>
+        <v>1029965</v>
       </c>
       <c r="BJ33" s="4">
         <f t="shared" si="22"/>
-        <v>1.004260945364345</v>
+        <v>1.0042619204090508</v>
       </c>
     </row>
     <row r="34" spans="1:62" x14ac:dyDescent="0.3">
@@ -6484,14 +6484,14 @@
       </c>
       <c r="E36" s="3">
         <f t="shared" si="0"/>
-        <v>280756</v>
+        <v>280763</v>
       </c>
       <c r="F36" s="5">
-        <v>767042</v>
+        <v>767049</v>
       </c>
       <c r="G36" s="4">
         <f t="shared" si="1"/>
-        <v>0.95385319423839554</v>
+        <v>0.95386189907119434</v>
       </c>
       <c r="H36" s="5">
         <v>814447</v>
@@ -6501,14 +6501,14 @@
       </c>
       <c r="J36" s="3">
         <f t="shared" si="2"/>
-        <v>265482</v>
+        <v>265490</v>
       </c>
       <c r="K36" s="5">
-        <v>778892</v>
+        <v>778900</v>
       </c>
       <c r="L36" s="4">
         <f t="shared" si="3"/>
-        <v>0.9563446117426917</v>
+        <v>0.95635443435852796</v>
       </c>
       <c r="M36" s="9">
         <v>1485608</v>
@@ -6520,11 +6520,11 @@
         <v>1417521</v>
       </c>
       <c r="P36" s="5">
-        <v>1420028</v>
+        <v>1420040</v>
       </c>
       <c r="Q36" s="4">
         <f t="shared" si="4"/>
-        <v>0.95585645742349257</v>
+        <v>0.95586453492442147</v>
       </c>
       <c r="R36" s="5">
         <v>815623</v>
@@ -6534,14 +6534,14 @@
       </c>
       <c r="T36" s="3">
         <f t="shared" si="5"/>
-        <v>268199</v>
+        <v>268205</v>
       </c>
       <c r="U36" s="5">
-        <v>778554</v>
+        <v>778560</v>
       </c>
       <c r="V36" s="4">
         <f t="shared" si="6"/>
-        <v>0.95455130617944806</v>
+        <v>0.95455866251932575</v>
       </c>
       <c r="W36" s="5">
         <v>826349</v>
@@ -6551,14 +6551,14 @@
       </c>
       <c r="Y36" s="3">
         <f t="shared" si="7"/>
-        <v>288621</v>
+        <v>288627</v>
       </c>
       <c r="Z36" s="5">
-        <v>788773</v>
+        <v>788779</v>
       </c>
       <c r="AA36" s="4">
         <f t="shared" si="8"/>
-        <v>0.95452768745409022</v>
+        <v>0.9545349483087654</v>
       </c>
       <c r="AB36" s="5">
         <v>1500292</v>
@@ -6568,14 +6568,14 @@
       </c>
       <c r="AD36" s="3">
         <f t="shared" si="9"/>
-        <v>549433</v>
+        <v>549441</v>
       </c>
       <c r="AE36" s="5">
-        <v>1455749</v>
+        <v>1455757</v>
       </c>
       <c r="AF36" s="4">
         <f t="shared" si="10"/>
-        <v>0.97031044623313323</v>
+        <v>0.97031577852844642</v>
       </c>
       <c r="AG36" s="5">
         <v>833041</v>
@@ -6585,14 +6585,14 @@
       </c>
       <c r="AI36" s="3">
         <f t="shared" si="11"/>
-        <v>255504</v>
+        <v>255509</v>
       </c>
       <c r="AJ36" s="5">
-        <v>802889</v>
+        <v>802894</v>
       </c>
       <c r="AK36" s="4">
         <f t="shared" si="12"/>
-        <v>0.96380490275988817</v>
+        <v>0.96381090486542675</v>
       </c>
       <c r="AL36" s="5">
         <v>845911</v>
@@ -6602,14 +6602,14 @@
       </c>
       <c r="AN36" s="3">
         <f t="shared" si="13"/>
-        <v>252981</v>
+        <v>252986</v>
       </c>
       <c r="AO36" s="5">
-        <v>815216</v>
+        <v>815221</v>
       </c>
       <c r="AP36" s="4">
         <f t="shared" si="14"/>
-        <v>0.96371367673431363</v>
+        <v>0.96371958752161868</v>
       </c>
       <c r="AQ36" s="3">
         <v>1519147</v>
@@ -6619,14 +6619,14 @@
       </c>
       <c r="AS36" s="3">
         <f t="shared" si="15"/>
-        <v>450268</v>
+        <v>450276</v>
       </c>
       <c r="AT36" s="3">
-        <v>1477408</v>
+        <v>1477416</v>
       </c>
       <c r="AU36" s="4">
         <f t="shared" si="16"/>
-        <v>0.97252471288163689</v>
+        <v>0.97252997899479121</v>
       </c>
       <c r="AV36" s="5">
         <v>864672</v>
@@ -6636,14 +6636,14 @@
       </c>
       <c r="AX36" s="3">
         <f t="shared" si="17"/>
-        <v>218895</v>
+        <v>218900</v>
       </c>
       <c r="AY36" s="5">
-        <v>817756</v>
+        <v>817761</v>
       </c>
       <c r="AZ36" s="4">
         <f t="shared" si="18"/>
-        <v>0.94574127530439289</v>
+        <v>0.94574705784389923</v>
       </c>
       <c r="BA36" s="10">
         <v>838532</v>
@@ -6653,14 +6653,14 @@
       </c>
       <c r="BC36" s="3">
         <f t="shared" si="19"/>
-        <v>226539</v>
+        <v>226544</v>
       </c>
       <c r="BD36" s="5">
-        <v>830293</v>
+        <v>830298</v>
       </c>
       <c r="BE36" s="4">
         <f t="shared" si="20"/>
-        <v>0.99017449542772373</v>
+        <v>0.99018045822938183</v>
       </c>
       <c r="BF36" s="10">
         <v>1502094</v>
@@ -6670,14 +6670,14 @@
       </c>
       <c r="BH36" s="3">
         <f t="shared" si="23"/>
-        <v>507878</v>
+        <v>507884</v>
       </c>
       <c r="BI36" s="5">
-        <v>1498528</v>
+        <v>1498534</v>
       </c>
       <c r="BJ36" s="4">
         <f t="shared" si="24"/>
-        <v>0.99762598079747344</v>
+        <v>0.99762997522125774</v>
       </c>
     </row>
     <row r="37" spans="1:62" x14ac:dyDescent="0.3">
@@ -6695,14 +6695,14 @@
       </c>
       <c r="E37" s="3">
         <f t="shared" si="0"/>
-        <v>268704</v>
+        <v>268709</v>
       </c>
       <c r="F37" s="5">
-        <v>609921</v>
+        <v>609926</v>
       </c>
       <c r="G37" s="4">
         <f t="shared" si="1"/>
-        <v>0.93742132709944259</v>
+        <v>0.93742901187605376</v>
       </c>
       <c r="H37" s="5">
         <v>656039</v>
@@ -6712,14 +6712,14 @@
       </c>
       <c r="J37" s="3">
         <f t="shared" si="2"/>
-        <v>249943</v>
+        <v>249949</v>
       </c>
       <c r="K37" s="5">
-        <v>615212</v>
+        <v>615218</v>
       </c>
       <c r="L37" s="4">
         <f t="shared" si="3"/>
-        <v>0.93776741931501029</v>
+        <v>0.93777656511274488</v>
       </c>
       <c r="M37" s="9">
         <v>844882</v>
@@ -6731,11 +6731,11 @@
         <v>786859</v>
       </c>
       <c r="P37" s="5">
-        <v>789086</v>
+        <v>789094</v>
       </c>
       <c r="Q37" s="4">
         <f t="shared" si="4"/>
-        <v>0.9339600086165879</v>
+        <v>0.93396947739447644</v>
       </c>
       <c r="R37" s="5">
         <v>664863</v>
@@ -6745,14 +6745,14 @@
       </c>
       <c r="T37" s="3">
         <f t="shared" si="5"/>
-        <v>256861</v>
+        <v>256868</v>
       </c>
       <c r="U37" s="5">
-        <v>621988</v>
+        <v>621995</v>
       </c>
       <c r="V37" s="4">
         <f t="shared" si="6"/>
-        <v>0.93551303050402868</v>
+        <v>0.93552355898884432</v>
       </c>
       <c r="W37" s="5">
         <v>670009</v>
@@ -6762,14 +6762,14 @@
       </c>
       <c r="Y37" s="3">
         <f t="shared" si="7"/>
-        <v>275180</v>
+        <v>275188</v>
       </c>
       <c r="Z37" s="5">
-        <v>628425</v>
+        <v>628433</v>
       </c>
       <c r="AA37" s="4">
         <f t="shared" si="8"/>
-        <v>0.93793516206498717</v>
+        <v>0.93794710220310473</v>
       </c>
       <c r="AB37" s="5">
         <v>858143</v>
@@ -6779,14 +6779,14 @@
       </c>
       <c r="AD37" s="3">
         <f t="shared" si="9"/>
-        <v>383166</v>
+        <v>383174</v>
       </c>
       <c r="AE37" s="5">
-        <v>819537</v>
+        <v>819545</v>
       </c>
       <c r="AF37" s="4">
         <f t="shared" si="10"/>
-        <v>0.95501215997799904</v>
+        <v>0.95502148243358043</v>
       </c>
       <c r="AG37" s="5">
         <v>675943</v>
@@ -6796,14 +6796,14 @@
       </c>
       <c r="AI37" s="3">
         <f t="shared" si="11"/>
-        <v>251711</v>
+        <v>251715</v>
       </c>
       <c r="AJ37" s="5">
-        <v>644688</v>
+        <v>644692</v>
       </c>
       <c r="AK37" s="4">
         <f t="shared" si="12"/>
-        <v>0.95376089403988207</v>
+        <v>0.95376681169861954</v>
       </c>
       <c r="AL37" s="5">
         <v>678429</v>
@@ -6813,14 +6813,14 @@
       </c>
       <c r="AN37" s="3">
         <f t="shared" si="13"/>
-        <v>248279</v>
+        <v>248283</v>
       </c>
       <c r="AO37" s="5">
-        <v>650797</v>
+        <v>650801</v>
       </c>
       <c r="AP37" s="4">
         <f t="shared" si="14"/>
-        <v>0.95927060900993322</v>
+        <v>0.95927650498430939</v>
       </c>
       <c r="AQ37" s="3">
         <v>865622</v>
@@ -6830,14 +6830,14 @@
       </c>
       <c r="AS37" s="3">
         <f t="shared" si="15"/>
-        <v>315000</v>
+        <v>315007</v>
       </c>
       <c r="AT37" s="3">
-        <v>834244</v>
+        <v>834251</v>
       </c>
       <c r="AU37" s="4">
         <f t="shared" si="16"/>
-        <v>0.96375092130283191</v>
+        <v>0.96375900797345726</v>
       </c>
       <c r="AV37" s="5">
         <v>690116</v>
@@ -6847,14 +6847,14 @@
       </c>
       <c r="AX37" s="3">
         <f t="shared" si="17"/>
-        <v>235071</v>
+        <v>235075</v>
       </c>
       <c r="AY37" s="5">
-        <v>658597</v>
+        <v>658601</v>
       </c>
       <c r="AZ37" s="4">
         <f t="shared" si="18"/>
-        <v>0.9543279680517478</v>
+        <v>0.95433376417877569</v>
       </c>
       <c r="BA37" s="10">
         <v>673244</v>
@@ -6864,14 +6864,14 @@
       </c>
       <c r="BC37" s="3">
         <f t="shared" si="19"/>
-        <v>241655</v>
+        <v>241659</v>
       </c>
       <c r="BD37" s="5">
-        <v>665222</v>
+        <v>665226</v>
       </c>
       <c r="BE37" s="4">
         <f t="shared" si="20"/>
-        <v>0.98808455775320692</v>
+        <v>0.98809049913552882</v>
       </c>
       <c r="BF37" s="10">
         <v>856336</v>
@@ -6881,14 +6881,14 @@
       </c>
       <c r="BH37" s="3">
         <f t="shared" si="23"/>
-        <v>356974</v>
+        <v>356979</v>
       </c>
       <c r="BI37" s="5">
-        <v>848357</v>
+        <v>848362</v>
       </c>
       <c r="BJ37" s="4">
         <f t="shared" si="24"/>
-        <v>0.99068239569514771</v>
+        <v>0.99068823452476595</v>
       </c>
     </row>
     <row r="38" spans="1:62" x14ac:dyDescent="0.3">
@@ -7024,14 +7024,14 @@
       </c>
       <c r="AN38" s="3">
         <f t="shared" si="13"/>
-        <v>9527</v>
+        <v>9528</v>
       </c>
       <c r="AO38" s="5">
-        <v>22352</v>
+        <v>22353</v>
       </c>
       <c r="AP38" s="4">
         <f t="shared" si="14"/>
-        <v>0.88215328755229305</v>
+        <v>0.88219275396637464</v>
       </c>
       <c r="AQ38" s="3">
         <v>38074</v>
@@ -7328,14 +7328,14 @@
       </c>
       <c r="E40" s="3">
         <f t="shared" si="0"/>
-        <v>105550</v>
+        <v>105554</v>
       </c>
       <c r="F40" s="5">
-        <v>258597</v>
+        <v>258601</v>
       </c>
       <c r="G40" s="4">
         <f t="shared" si="1"/>
-        <v>0.94558265899758298</v>
+        <v>0.94559728534914933</v>
       </c>
       <c r="H40" s="5">
         <v>275367</v>
@@ -7345,14 +7345,14 @@
       </c>
       <c r="J40" s="3">
         <f t="shared" si="2"/>
-        <v>98775</v>
+        <v>98780</v>
       </c>
       <c r="K40" s="5">
-        <v>260337</v>
+        <v>260342</v>
       </c>
       <c r="L40" s="4">
         <f t="shared" si="3"/>
-        <v>0.94541829631001539</v>
+        <v>0.94543645389607323</v>
       </c>
       <c r="M40" s="9">
         <v>339208</v>
@@ -7364,11 +7364,11 @@
         <v>320573</v>
       </c>
       <c r="P40" s="5">
-        <v>321304</v>
+        <v>321313</v>
       </c>
       <c r="Q40" s="4">
         <f t="shared" si="4"/>
-        <v>0.9472182259852362</v>
+        <v>0.9472447583783401</v>
       </c>
       <c r="R40" s="5">
         <v>277547</v>
@@ -7378,14 +7378,14 @@
       </c>
       <c r="T40" s="3">
         <f t="shared" si="5"/>
-        <v>97305</v>
+        <v>97309</v>
       </c>
       <c r="U40" s="5">
-        <v>262679</v>
+        <v>262683</v>
       </c>
       <c r="V40" s="4">
         <f t="shared" si="6"/>
-        <v>0.9464306946210912</v>
+        <v>0.94644510659455872</v>
       </c>
       <c r="W40" s="5">
         <v>278758</v>
@@ -7395,14 +7395,14 @@
       </c>
       <c r="Y40" s="3">
         <f t="shared" si="7"/>
-        <v>125355</v>
+        <v>125359</v>
       </c>
       <c r="Z40" s="5">
-        <v>265229</v>
+        <v>265233</v>
       </c>
       <c r="AA40" s="4">
         <f t="shared" si="8"/>
-        <v>0.9514668637312651</v>
+        <v>0.95148121309522959</v>
       </c>
       <c r="AB40" s="5">
         <v>343140</v>
@@ -7412,14 +7412,14 @@
       </c>
       <c r="AD40" s="3">
         <f t="shared" si="9"/>
-        <v>142738</v>
+        <v>142747</v>
       </c>
       <c r="AE40" s="5">
-        <v>328434</v>
+        <v>328443</v>
       </c>
       <c r="AF40" s="4">
         <f t="shared" si="10"/>
-        <v>0.95714285714285718</v>
+        <v>0.95716908550445878</v>
       </c>
       <c r="AG40" s="5">
         <v>282101</v>
@@ -7429,14 +7429,14 @@
       </c>
       <c r="AI40" s="3">
         <f t="shared" si="11"/>
-        <v>100027</v>
+        <v>100031</v>
       </c>
       <c r="AJ40" s="5">
-        <v>268723</v>
+        <v>268727</v>
       </c>
       <c r="AK40" s="4">
         <f t="shared" si="12"/>
-        <v>0.95257726842513857</v>
+        <v>0.95259144774389315</v>
       </c>
       <c r="AL40" s="5">
         <v>282756</v>
@@ -7446,14 +7446,14 @@
       </c>
       <c r="AN40" s="3">
         <f t="shared" si="13"/>
-        <v>99035</v>
+        <v>99040</v>
       </c>
       <c r="AO40" s="5">
-        <v>270982</v>
+        <v>270987</v>
       </c>
       <c r="AP40" s="4">
         <f t="shared" si="14"/>
-        <v>0.95835985796941536</v>
+        <v>0.95837754106013662</v>
       </c>
       <c r="AQ40" s="3">
         <v>343988</v>
@@ -7463,14 +7463,14 @@
       </c>
       <c r="AS40" s="3">
         <f t="shared" si="15"/>
-        <v>125872</v>
+        <v>125882</v>
       </c>
       <c r="AT40" s="3">
-        <v>332735</v>
+        <v>332745</v>
       </c>
       <c r="AU40" s="4">
         <f t="shared" si="16"/>
-        <v>0.96728664953428611</v>
+        <v>0.96731572031582502</v>
       </c>
       <c r="AV40" s="5">
         <v>285285</v>
@@ -7480,14 +7480,14 @@
       </c>
       <c r="AX40" s="3">
         <f t="shared" si="17"/>
-        <v>94351</v>
+        <v>94356</v>
       </c>
       <c r="AY40" s="5">
-        <v>273397</v>
+        <v>273402</v>
       </c>
       <c r="AZ40" s="4">
         <f t="shared" si="18"/>
-        <v>0.95832938990833727</v>
+        <v>0.95834691624165314</v>
       </c>
       <c r="BA40" s="10">
         <v>276279</v>
@@ -7497,14 +7497,14 @@
       </c>
       <c r="BC40" s="3">
         <f t="shared" si="19"/>
-        <v>95266</v>
+        <v>95269</v>
       </c>
       <c r="BD40" s="5">
-        <v>275450</v>
+        <v>275453</v>
       </c>
       <c r="BE40" s="4">
         <f t="shared" si="20"/>
-        <v>0.99699941001668602</v>
+        <v>0.99701026860528663</v>
       </c>
       <c r="BF40" s="10">
         <v>339189</v>
@@ -7514,14 +7514,14 @@
       </c>
       <c r="BH40" s="3">
         <f t="shared" si="23"/>
-        <v>141278</v>
+        <v>141281</v>
       </c>
       <c r="BI40" s="5">
-        <v>337579</v>
+        <v>337582</v>
       </c>
       <c r="BJ40" s="4">
         <f t="shared" si="24"/>
-        <v>0.99525338380666828</v>
+        <v>0.99526222843311551</v>
       </c>
     </row>
     <row r="41" spans="1:62" x14ac:dyDescent="0.3">
@@ -7539,14 +7539,14 @@
       </c>
       <c r="E41" s="3">
         <f t="shared" si="0"/>
-        <v>326737</v>
+        <v>326747</v>
       </c>
       <c r="F41" s="5">
-        <v>832961</v>
+        <v>832971</v>
       </c>
       <c r="G41" s="4">
         <f t="shared" si="1"/>
-        <v>0.95447524321351229</v>
+        <v>0.95448670203623276</v>
       </c>
       <c r="H41" s="5">
         <v>878008</v>
@@ -7556,14 +7556,14 @@
       </c>
       <c r="J41" s="3">
         <f t="shared" si="2"/>
-        <v>326541</v>
+        <v>326550</v>
       </c>
       <c r="K41" s="5">
-        <v>839665</v>
+        <v>839674</v>
       </c>
       <c r="L41" s="4">
         <f t="shared" si="3"/>
-        <v>0.95632955508378059</v>
+        <v>0.9563398055598582</v>
       </c>
       <c r="M41" s="9">
         <v>999035</v>
@@ -7575,11 +7575,11 @@
         <v>948683</v>
       </c>
       <c r="P41" s="5">
-        <v>951030</v>
+        <v>951047</v>
       </c>
       <c r="Q41" s="4">
         <f t="shared" si="4"/>
-        <v>0.95194863042836342</v>
+        <v>0.95196564684920948</v>
       </c>
       <c r="R41" s="5">
         <v>889467</v>
@@ -7589,14 +7589,14 @@
       </c>
       <c r="T41" s="3">
         <f t="shared" si="5"/>
-        <v>328425</v>
+        <v>328439</v>
       </c>
       <c r="U41" s="5">
-        <v>849409</v>
+        <v>849423</v>
       </c>
       <c r="V41" s="4">
         <f t="shared" si="6"/>
-        <v>0.95496404026231441</v>
+        <v>0.95497978002556583</v>
       </c>
       <c r="W41" s="5">
         <v>894020</v>
@@ -7606,14 +7606,14 @@
       </c>
       <c r="Y41" s="3">
         <f t="shared" si="7"/>
-        <v>361360</v>
+        <v>361373</v>
       </c>
       <c r="Z41" s="5">
-        <v>855298</v>
+        <v>855311</v>
       </c>
       <c r="AA41" s="4">
         <f t="shared" si="8"/>
-        <v>0.9566877698485492</v>
+        <v>0.95670231091027047</v>
       </c>
       <c r="AB41" s="5">
         <v>1012178</v>
@@ -7623,14 +7623,14 @@
       </c>
       <c r="AD41" s="3">
         <f t="shared" si="9"/>
-        <v>420726</v>
+        <v>420738</v>
       </c>
       <c r="AE41" s="5">
-        <v>977776</v>
+        <v>977788</v>
       </c>
       <c r="AF41" s="4">
         <f t="shared" si="10"/>
-        <v>0.96601190699659545</v>
+        <v>0.96602376261882794</v>
       </c>
       <c r="AG41" s="5">
         <v>904846</v>
@@ -7640,14 +7640,14 @@
       </c>
       <c r="AI41" s="3">
         <f t="shared" si="11"/>
-        <v>322130</v>
+        <v>322142</v>
       </c>
       <c r="AJ41" s="5">
-        <v>873186</v>
+        <v>873198</v>
       </c>
       <c r="AK41" s="4">
         <f t="shared" si="12"/>
-        <v>0.96501062059179132</v>
+        <v>0.96502388251702498</v>
       </c>
       <c r="AL41" s="5">
         <v>910192</v>
@@ -7657,14 +7657,14 @@
       </c>
       <c r="AN41" s="3">
         <f t="shared" si="13"/>
-        <v>324183</v>
+        <v>324196</v>
       </c>
       <c r="AO41" s="5">
-        <v>879158</v>
+        <v>879171</v>
       </c>
       <c r="AP41" s="4">
         <f t="shared" si="14"/>
-        <v>0.9659038971997117</v>
+        <v>0.96591817990050455</v>
       </c>
       <c r="AQ41" s="3">
         <v>1025826</v>
@@ -7674,14 +7674,14 @@
       </c>
       <c r="AS41" s="3">
         <f t="shared" si="15"/>
-        <v>359868</v>
+        <v>359885</v>
       </c>
       <c r="AT41" s="3">
-        <v>993446</v>
+        <v>993463</v>
       </c>
       <c r="AU41" s="4">
         <f t="shared" si="16"/>
-        <v>0.96843519271299416</v>
+        <v>0.968451764724232</v>
       </c>
       <c r="AV41" s="5">
         <v>923071</v>
@@ -7691,14 +7691,14 @@
       </c>
       <c r="AX41" s="3">
         <f t="shared" si="17"/>
-        <v>308208</v>
+        <v>308220</v>
       </c>
       <c r="AY41" s="5">
-        <v>890934</v>
+        <v>890946</v>
       </c>
       <c r="AZ41" s="4">
         <f t="shared" si="18"/>
-        <v>0.96518469326844847</v>
+        <v>0.96519769335186567</v>
       </c>
       <c r="BA41" s="11">
         <v>907892</v>
@@ -7708,14 +7708,14 @@
       </c>
       <c r="BC41" s="3">
         <f t="shared" si="19"/>
-        <v>315671</v>
+        <v>315681</v>
       </c>
       <c r="BD41" s="5">
-        <v>897979</v>
+        <v>897989</v>
       </c>
       <c r="BE41" s="4">
         <f t="shared" si="20"/>
-        <v>0.98908130041899256</v>
+        <v>0.98909231494494942</v>
       </c>
       <c r="BF41" s="11">
         <v>1023930</v>
@@ -7725,14 +7725,14 @@
       </c>
       <c r="BH41" s="3">
         <f t="shared" si="23"/>
-        <v>403390</v>
+        <v>403399</v>
       </c>
       <c r="BI41" s="5">
-        <v>1012297</v>
+        <v>1012306</v>
       </c>
       <c r="BJ41" s="4">
         <f t="shared" si="24"/>
-        <v>0.98863887179787679</v>
+        <v>0.98864766146123273</v>
       </c>
     </row>
     <row r="42" spans="1:62" x14ac:dyDescent="0.3">
@@ -7961,14 +7961,14 @@
       </c>
       <c r="E43" s="3">
         <f t="shared" si="0"/>
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="F43" s="5">
-        <v>3157</v>
+        <v>3158</v>
       </c>
       <c r="G43" s="4">
         <f t="shared" si="1"/>
-        <v>0.94070321811680568</v>
+        <v>0.94100119189511322</v>
       </c>
       <c r="H43" s="5">
         <v>3369</v>
@@ -7978,14 +7978,14 @@
       </c>
       <c r="J43" s="3">
         <f t="shared" si="2"/>
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="K43" s="5">
-        <v>3202</v>
+        <v>3203</v>
       </c>
       <c r="L43" s="4">
         <f t="shared" si="3"/>
-        <v>0.95043039477589786</v>
+        <v>0.95072721875927579</v>
       </c>
       <c r="M43" s="9">
         <v>4189</v>
@@ -7997,11 +7997,11 @@
         <v>4005</v>
       </c>
       <c r="P43" s="5">
-        <v>4014</v>
+        <v>4015</v>
       </c>
       <c r="Q43" s="4">
         <f t="shared" si="4"/>
-        <v>0.95822391978992605</v>
+        <v>0.95846264024826933</v>
       </c>
       <c r="R43" s="5">
         <v>3398</v>
@@ -8011,14 +8011,14 @@
       </c>
       <c r="T43" s="3">
         <f t="shared" si="5"/>
-        <v>1908</v>
+        <v>1909</v>
       </c>
       <c r="U43" s="5">
-        <v>3263</v>
+        <v>3264</v>
       </c>
       <c r="V43" s="4">
         <f t="shared" si="6"/>
-        <v>0.96027074749852859</v>
+        <v>0.96056503825779871</v>
       </c>
       <c r="W43" s="5">
         <v>3433</v>
@@ -8028,14 +8028,14 @@
       </c>
       <c r="Y43" s="3">
         <f t="shared" si="7"/>
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="Z43" s="5">
-        <v>3321</v>
+        <v>3322</v>
       </c>
       <c r="AA43" s="4">
         <f t="shared" si="8"/>
-        <v>0.96737547334692686</v>
+        <v>0.96766676376347216</v>
       </c>
       <c r="AB43" s="5">
         <v>4306</v>
@@ -8045,14 +8045,14 @@
       </c>
       <c r="AD43" s="3">
         <f t="shared" si="9"/>
-        <v>2536</v>
+        <v>2537</v>
       </c>
       <c r="AE43" s="5">
-        <v>4185</v>
+        <v>4186</v>
       </c>
       <c r="AF43" s="4">
         <f t="shared" si="10"/>
-        <v>0.97189967487227125</v>
+        <v>0.97213190896423596</v>
       </c>
       <c r="AG43" s="5">
         <v>3505</v>
@@ -8062,14 +8062,14 @@
       </c>
       <c r="AI43" s="3">
         <f t="shared" si="11"/>
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="AJ43" s="5">
-        <v>3340</v>
+        <v>3341</v>
       </c>
       <c r="AK43" s="4">
         <f t="shared" si="12"/>
-        <v>0.95292439372325255</v>
+        <v>0.95320970042796005</v>
       </c>
       <c r="AL43" s="5">
         <v>3511</v>
@@ -8079,14 +8079,14 @@
       </c>
       <c r="AN43" s="3">
         <f t="shared" si="13"/>
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="AO43" s="5">
-        <v>3373</v>
+        <v>3374</v>
       </c>
       <c r="AP43" s="4">
         <f t="shared" si="14"/>
-        <v>0.96069495870122468</v>
+        <v>0.96097977784107091</v>
       </c>
       <c r="AQ43" s="3">
         <v>4405</v>
@@ -8096,14 +8096,14 @@
       </c>
       <c r="AS43" s="3">
         <f t="shared" si="15"/>
-        <v>2281</v>
+        <v>2282</v>
       </c>
       <c r="AT43" s="3">
-        <v>4269</v>
+        <v>4270</v>
       </c>
       <c r="AU43" s="4">
         <f t="shared" si="16"/>
-        <v>0.96912599318955728</v>
+        <v>0.96935300794551649</v>
       </c>
       <c r="AV43" s="5">
         <v>3534</v>
@@ -8113,14 +8113,14 @@
       </c>
       <c r="AX43" s="3">
         <f t="shared" si="17"/>
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="AY43" s="5">
-        <v>3400</v>
+        <v>3401</v>
       </c>
       <c r="AZ43" s="4">
         <f t="shared" si="18"/>
-        <v>0.96208262591963778</v>
+        <v>0.9623655913978495</v>
       </c>
       <c r="BA43" s="10">
         <v>3464</v>
@@ -8130,14 +8130,14 @@
       </c>
       <c r="BC43" s="3">
         <f t="shared" si="19"/>
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="BD43" s="5">
-        <v>3453</v>
+        <v>3454</v>
       </c>
       <c r="BE43" s="4">
         <f t="shared" si="20"/>
-        <v>0.99682448036951499</v>
+        <v>0.99711316397228633</v>
       </c>
       <c r="BF43" s="10">
         <v>4361</v>
@@ -8147,14 +8147,14 @@
       </c>
       <c r="BH43" s="3">
         <f t="shared" si="23"/>
-        <v>2589</v>
+        <v>2590</v>
       </c>
       <c r="BI43" s="5">
-        <v>4340</v>
+        <v>4341</v>
       </c>
       <c r="BJ43" s="4">
         <f t="shared" si="24"/>
-        <v>0.9951845906902087</v>
+        <v>0.99541389589543683</v>
       </c>
     </row>
     <row r="44" spans="1:62" x14ac:dyDescent="0.3">
@@ -8172,14 +8172,14 @@
       </c>
       <c r="E44" s="3">
         <f t="shared" si="0"/>
-        <v>151691</v>
+        <v>151692</v>
       </c>
       <c r="F44" s="5">
-        <v>296323</v>
+        <v>296324</v>
       </c>
       <c r="G44" s="4">
         <f t="shared" si="1"/>
-        <v>0.87116158602016192</v>
+        <v>0.87116452592555571</v>
       </c>
       <c r="H44" s="5">
         <v>343940</v>
@@ -8189,14 +8189,14 @@
       </c>
       <c r="J44" s="3">
         <f t="shared" si="2"/>
-        <v>148676</v>
+        <v>148677</v>
       </c>
       <c r="K44" s="5">
-        <v>299526</v>
+        <v>299527</v>
       </c>
       <c r="L44" s="4">
         <f t="shared" si="3"/>
-        <v>0.87086701168808511</v>
+        <v>0.87086991917194856</v>
       </c>
       <c r="M44" s="9">
         <v>415294</v>
@@ -8208,11 +8208,11 @@
         <v>362232</v>
       </c>
       <c r="P44" s="5">
-        <v>363097</v>
+        <v>363098</v>
       </c>
       <c r="Q44" s="4">
         <f t="shared" si="4"/>
-        <v>0.87431313719918902</v>
+        <v>0.87431554513188248</v>
       </c>
       <c r="R44" s="5">
         <v>349377</v>
@@ -8222,14 +8222,14 @@
       </c>
       <c r="T44" s="3">
         <f t="shared" si="5"/>
-        <v>152722</v>
+        <v>152723</v>
       </c>
       <c r="U44" s="5">
-        <v>304261</v>
+        <v>304262</v>
       </c>
       <c r="V44" s="4">
         <f t="shared" si="6"/>
-        <v>0.87086728662733948</v>
+        <v>0.87087014886497971</v>
       </c>
       <c r="W44" s="5">
         <v>352323</v>
@@ -8239,14 +8239,14 @@
       </c>
       <c r="Y44" s="3">
         <f t="shared" si="7"/>
-        <v>164142</v>
+        <v>164143</v>
       </c>
       <c r="Z44" s="5">
-        <v>307802</v>
+        <v>307803</v>
       </c>
       <c r="AA44" s="4">
         <f t="shared" si="8"/>
-        <v>0.8736358398401467</v>
+        <v>0.87363867814477059</v>
       </c>
       <c r="AB44" s="5">
         <v>424236</v>
@@ -8256,14 +8256,14 @@
       </c>
       <c r="AD44" s="3">
         <f t="shared" si="9"/>
-        <v>208464</v>
+        <v>208465</v>
       </c>
       <c r="AE44" s="5">
-        <v>382950</v>
+        <v>382951</v>
       </c>
       <c r="AF44" s="4">
         <f t="shared" si="10"/>
-        <v>0.90268152632025567</v>
+        <v>0.90268388349880724</v>
       </c>
       <c r="AG44" s="5">
         <v>358309</v>
@@ -8273,14 +8273,14 @@
       </c>
       <c r="AI44" s="3">
         <f t="shared" si="11"/>
-        <v>154201</v>
+        <v>154202</v>
       </c>
       <c r="AJ44" s="5">
-        <v>319720</v>
+        <v>319721</v>
       </c>
       <c r="AK44" s="4">
         <f t="shared" si="12"/>
-        <v>0.89230245402711073</v>
+        <v>0.89230524491430585</v>
       </c>
       <c r="AL44" s="5">
         <v>359722</v>
@@ -8290,14 +8290,14 @@
       </c>
       <c r="AN44" s="3">
         <f t="shared" si="13"/>
-        <v>150217</v>
+        <v>150218</v>
       </c>
       <c r="AO44" s="5">
-        <v>323558</v>
+        <v>323559</v>
       </c>
       <c r="AP44" s="4">
         <f t="shared" si="14"/>
-        <v>0.89946681048142729</v>
+        <v>0.89946959040592456</v>
       </c>
       <c r="AQ44" s="3">
         <v>432157</v>
@@ -8307,14 +8307,14 @@
       </c>
       <c r="AS44" s="3">
         <f t="shared" si="15"/>
-        <v>178601</v>
+        <v>178602</v>
       </c>
       <c r="AT44" s="3">
-        <v>391668</v>
+        <v>391669</v>
       </c>
       <c r="AU44" s="4">
         <f t="shared" si="16"/>
-        <v>0.90630951251512759</v>
+        <v>0.90631182648898434</v>
       </c>
       <c r="AV44" s="5">
         <v>367733</v>
@@ -8324,14 +8324,14 @@
       </c>
       <c r="AX44" s="3">
         <f t="shared" si="17"/>
-        <v>145696</v>
+        <v>145697</v>
       </c>
       <c r="AY44" s="5">
-        <v>327666</v>
+        <v>327667</v>
       </c>
       <c r="AZ44" s="4">
         <f t="shared" si="18"/>
-        <v>0.89104322973461725</v>
+        <v>0.89104594909893864</v>
       </c>
       <c r="BA44" s="10">
         <v>337773</v>
@@ -8341,14 +8341,14 @@
       </c>
       <c r="BC44" s="3">
         <f t="shared" si="19"/>
-        <v>150760</v>
+        <v>150761</v>
       </c>
       <c r="BD44" s="5">
-        <v>331428</v>
+        <v>331429</v>
       </c>
       <c r="BE44" s="4">
         <f t="shared" si="20"/>
-        <v>0.98121519482018993</v>
+        <v>0.98121815538838209</v>
       </c>
       <c r="BF44" s="10">
         <v>408499</v>
@@ -8358,14 +8358,14 @@
       </c>
       <c r="BH44" s="3">
         <f t="shared" si="23"/>
-        <v>201491</v>
+        <v>201492</v>
       </c>
       <c r="BI44" s="5">
-        <v>400225</v>
+        <v>400226</v>
       </c>
       <c r="BJ44" s="4">
         <f t="shared" si="24"/>
-        <v>0.97974536045375871</v>
+        <v>0.97974780844016751</v>
       </c>
     </row>
     <row r="45" spans="1:62" x14ac:dyDescent="0.3">
@@ -8383,14 +8383,14 @@
       </c>
       <c r="E45" s="3">
         <f t="shared" si="0"/>
-        <v>112355</v>
+        <v>112358</v>
       </c>
       <c r="F45" s="5">
-        <v>232579</v>
+        <v>232582</v>
       </c>
       <c r="G45" s="4">
         <f t="shared" si="1"/>
-        <v>0.92967638264873764</v>
+        <v>0.9296883743984139</v>
       </c>
       <c r="H45" s="5">
         <v>249985</v>
@@ -8400,14 +8400,14 @@
       </c>
       <c r="J45" s="3">
         <f t="shared" si="2"/>
-        <v>104751</v>
+        <v>104755</v>
       </c>
       <c r="K45" s="5">
-        <v>234329</v>
+        <v>234333</v>
       </c>
       <c r="L45" s="4">
         <f t="shared" si="3"/>
-        <v>0.93737224233454008</v>
+        <v>0.93738824329459769</v>
       </c>
       <c r="M45" s="9">
         <v>300587</v>
@@ -8419,11 +8419,11 @@
         <v>284476</v>
       </c>
       <c r="P45" s="5">
-        <v>285017</v>
+        <v>285022</v>
       </c>
       <c r="Q45" s="4">
         <f t="shared" si="4"/>
-        <v>0.94820135268657657</v>
+        <v>0.94821798680581659</v>
       </c>
       <c r="R45" s="5">
         <v>247712</v>
@@ -8433,14 +8433,14 @@
       </c>
       <c r="T45" s="3">
         <f t="shared" si="5"/>
-        <v>109595</v>
+        <v>109600</v>
       </c>
       <c r="U45" s="5">
-        <v>235854</v>
+        <v>235859</v>
       </c>
       <c r="V45" s="4">
         <f t="shared" si="6"/>
-        <v>0.95212989277871074</v>
+        <v>0.95215007750936576</v>
       </c>
       <c r="W45" s="5">
         <v>250023</v>
@@ -8450,14 +8450,14 @@
       </c>
       <c r="Y45" s="3">
         <f t="shared" si="7"/>
-        <v>116275</v>
+        <v>116280</v>
       </c>
       <c r="Z45" s="5">
-        <v>237777</v>
+        <v>237782</v>
       </c>
       <c r="AA45" s="4">
         <f t="shared" si="8"/>
-        <v>0.95102050611343758</v>
+        <v>0.95104050427360687</v>
       </c>
       <c r="AB45" s="5">
         <v>306096</v>
@@ -8467,14 +8467,14 @@
       </c>
       <c r="AD45" s="3">
         <f t="shared" si="9"/>
-        <v>151899</v>
+        <v>151902</v>
       </c>
       <c r="AE45" s="5">
-        <v>293865</v>
+        <v>293868</v>
       </c>
       <c r="AF45" s="4">
         <f t="shared" si="10"/>
-        <v>0.96004194762427475</v>
+        <v>0.96005174847106789</v>
       </c>
       <c r="AG45" s="5">
         <v>252706</v>
@@ -8484,14 +8484,14 @@
       </c>
       <c r="AI45" s="3">
         <f t="shared" si="11"/>
-        <v>106722</v>
+        <v>106725</v>
       </c>
       <c r="AJ45" s="5">
-        <v>243712</v>
+        <v>243715</v>
       </c>
       <c r="AK45" s="4">
         <f t="shared" si="12"/>
-        <v>0.96440923444635263</v>
+        <v>0.96442110594920583</v>
       </c>
       <c r="AL45" s="5">
         <v>254538</v>
@@ -8501,14 +8501,14 @@
       </c>
       <c r="AN45" s="3">
         <f t="shared" si="13"/>
-        <v>96699</v>
+        <v>96702</v>
       </c>
       <c r="AO45" s="5">
-        <v>246026</v>
+        <v>246029</v>
       </c>
       <c r="AP45" s="4">
         <f t="shared" si="14"/>
-        <v>0.96655902065703347</v>
+        <v>0.96657080671648243</v>
       </c>
       <c r="AQ45" s="3">
         <v>310997</v>
@@ -8518,14 +8518,14 @@
       </c>
       <c r="AS45" s="3">
         <f t="shared" si="15"/>
-        <v>122784</v>
+        <v>122787</v>
       </c>
       <c r="AT45" s="3">
-        <v>299911</v>
+        <v>299914</v>
       </c>
       <c r="AU45" s="4">
         <f t="shared" si="16"/>
-        <v>0.96435335389087351</v>
+        <v>0.96436300028617639</v>
       </c>
       <c r="AV45" s="5">
         <v>259359</v>
@@ -8535,14 +8535,14 @@
       </c>
       <c r="AX45" s="3">
         <f t="shared" si="17"/>
-        <v>98680</v>
+        <v>98683</v>
       </c>
       <c r="AY45" s="5">
-        <v>248522</v>
+        <v>248525</v>
       </c>
       <c r="AZ45" s="4">
         <f t="shared" si="18"/>
-        <v>0.95821621767511445</v>
+        <v>0.95822778465370395</v>
       </c>
       <c r="BA45" s="10">
         <v>254394</v>
@@ -8552,14 +8552,14 @@
       </c>
       <c r="BC45" s="3">
         <f t="shared" si="19"/>
-        <v>102919</v>
+        <v>102921</v>
       </c>
       <c r="BD45" s="5">
-        <v>250487</v>
+        <v>250489</v>
       </c>
       <c r="BE45" s="4">
         <f t="shared" si="20"/>
-        <v>0.98464193337893191</v>
+        <v>0.9846497951995723</v>
       </c>
       <c r="BF45" s="10">
         <v>309142</v>
@@ -8569,14 +8569,14 @@
       </c>
       <c r="BH45" s="3">
         <f t="shared" si="23"/>
-        <v>148076</v>
+        <v>148079</v>
       </c>
       <c r="BI45" s="5">
-        <v>304829</v>
+        <v>304832</v>
       </c>
       <c r="BJ45" s="4">
         <f t="shared" si="24"/>
-        <v>0.98604848257435096</v>
+        <v>0.98605818685264379</v>
       </c>
     </row>
     <row r="46" spans="1:62" x14ac:dyDescent="0.3">
@@ -9016,15 +9016,15 @@
       </c>
       <c r="E48" s="8">
         <f>F48-D48</f>
-        <v>2892021</v>
+        <v>2892082</v>
       </c>
       <c r="F48" s="7">
         <f>SUM(F10:F47)</f>
-        <v>6970535</v>
+        <v>6970596</v>
       </c>
       <c r="G48" s="6">
         <f>F48/C48</f>
-        <v>0.94239680026087647</v>
+        <v>0.94240504728995189</v>
       </c>
       <c r="H48" s="7">
         <f>SUM(H10:H47)</f>
@@ -9036,15 +9036,15 @@
       </c>
       <c r="J48" s="8">
         <f t="shared" ref="J48" si="25">K48-I48</f>
-        <v>2779787</v>
+        <v>2779853</v>
       </c>
       <c r="K48" s="7">
         <f>SUM(K10:K47)</f>
-        <v>7078335</v>
+        <v>7078401</v>
       </c>
       <c r="L48" s="6">
         <f t="shared" ref="L48" si="26">K48/H48</f>
-        <v>0.944334527815059</v>
+        <v>0.94434333300425055</v>
       </c>
       <c r="M48" s="7">
         <f>SUM(M10:M47)</f>
@@ -9056,15 +9056,15 @@
       </c>
       <c r="O48" s="7">
         <f t="shared" ref="O48" si="27">P48-N48</f>
-        <v>4723285</v>
+        <v>4723391</v>
       </c>
       <c r="P48" s="7">
         <f>SUM(P10:P47)</f>
-        <v>11176336</v>
+        <v>11176442</v>
       </c>
       <c r="Q48" s="6">
         <f t="shared" ref="Q48" si="28">P48/M48</f>
-        <v>0.94385123811301297</v>
+        <v>0.94386018990465914</v>
       </c>
       <c r="R48" s="7">
         <f>SUM(R10:R47)</f>
@@ -9076,15 +9076,15 @@
       </c>
       <c r="T48" s="8">
         <f>U48-S48</f>
-        <v>2871488</v>
+        <v>2871563</v>
       </c>
       <c r="U48" s="7">
         <f>SUM(U10:U47)</f>
-        <v>7104543</v>
+        <v>7104618</v>
       </c>
       <c r="V48" s="6">
         <f>U48/R48</f>
-        <v>0.9418197658595483</v>
+        <v>0.94182970829813162</v>
       </c>
       <c r="W48" s="7">
         <f>SUM(W10:W47)</f>
@@ -9096,15 +9096,15 @@
       </c>
       <c r="Y48" s="8">
         <f t="shared" ref="Y48" si="29">Z48-X48</f>
-        <v>3037865</v>
+        <v>3037944</v>
       </c>
       <c r="Z48" s="7">
         <f>SUM(Z10:Z47)</f>
-        <v>7205440</v>
+        <v>7205519</v>
       </c>
       <c r="AA48" s="6">
         <f t="shared" ref="AA48" si="30">Z48/W48</f>
-        <v>0.94422333102173273</v>
+        <v>0.94423368342812997</v>
       </c>
       <c r="AB48" s="7">
         <f>SUM(AB10:AB47)</f>
@@ -9116,15 +9116,15 @@
       </c>
       <c r="AD48" s="8">
         <f>AE48-AC48</f>
-        <v>5143286</v>
+        <v>5143372</v>
       </c>
       <c r="AE48" s="7">
         <f>SUM(AE10:AE47)</f>
-        <v>11574097</v>
+        <v>11574183</v>
       </c>
       <c r="AF48" s="6">
         <f>AE48/AB48</f>
-        <v>0.96127004518612391</v>
+        <v>0.9612771877929196</v>
       </c>
       <c r="AG48" s="7">
         <f>SUM(AG10:AG47)</f>
@@ -9136,15 +9136,15 @@
       </c>
       <c r="AI48" s="8">
         <f>AJ48-AH48</f>
-        <v>2802544</v>
+        <v>2802611</v>
       </c>
       <c r="AJ48" s="7">
         <f>SUM(AJ10:AJ47)</f>
-        <v>7356288</v>
+        <v>7356355</v>
       </c>
       <c r="AK48" s="6">
         <f>AJ48/AG48</f>
-        <v>0.95454810871664497</v>
+        <v>0.95455680260183329</v>
       </c>
       <c r="AL48" s="7">
         <f>SUM(AL10:AL47)</f>
@@ -9156,15 +9156,15 @@
       </c>
       <c r="AN48" s="8">
         <f t="shared" ref="AN48" si="31">AO48-AM48</f>
-        <v>2784744</v>
+        <v>2784819</v>
       </c>
       <c r="AO48" s="7">
         <f>SUM(AO10:AO47)</f>
-        <v>7459880</v>
+        <v>7459955</v>
       </c>
       <c r="AP48" s="6">
         <f t="shared" ref="AP48" si="32">AO48/AL48</f>
-        <v>0.95648941709494617</v>
+        <v>0.95649903343009934</v>
       </c>
       <c r="AQ48" s="7">
         <f>SUM(AQ10:AQ47)</f>
@@ -9176,15 +9176,15 @@
       </c>
       <c r="AS48" s="8">
         <f>AT48-AR48</f>
-        <v>4440225</v>
+        <v>4440328</v>
       </c>
       <c r="AT48" s="7">
         <f>SUM(AT10:AT47)</f>
-        <v>11781171</v>
+        <v>11781274</v>
       </c>
       <c r="AU48" s="6">
         <f>AT48/AQ48</f>
-        <v>0.96328121148126888</v>
+        <v>0.96328963322175476</v>
       </c>
       <c r="AV48" s="7">
         <f>SUM(AV10:AV47)</f>
@@ -9196,15 +9196,15 @@
       </c>
       <c r="AX48" s="8">
         <f t="shared" ref="AX48" si="33">AY48-AW48</f>
-        <v>2608442</v>
+        <v>2608517</v>
       </c>
       <c r="AY48" s="7">
         <f>SUM(AY10:AY47)</f>
-        <v>7517208</v>
+        <v>7517283</v>
       </c>
       <c r="AZ48" s="6">
         <f t="shared" ref="AZ48" si="34">AY48/AV48</f>
-        <v>0.94125242334176307</v>
+        <v>0.94126181431933753</v>
       </c>
       <c r="BA48" s="7">
         <f>SUM(BA10:BA47)</f>
@@ -9216,15 +9216,15 @@
       </c>
       <c r="BC48" s="8">
         <f t="shared" ref="BC48" si="35">BD48-BB48</f>
-        <v>2771698</v>
+        <v>2771770</v>
       </c>
       <c r="BD48" s="7">
         <f>SUM(BD10:BD47)</f>
-        <v>7630067</v>
+        <v>7630139</v>
       </c>
       <c r="BE48" s="6">
         <f t="shared" ref="BE48" si="36">BD48/BA48</f>
-        <v>0.98816479076733232</v>
+        <v>0.98817411543839162</v>
       </c>
       <c r="BF48" s="7">
         <f>SUM(BF10:BF47)</f>
@@ -9236,15 +9236,15 @@
       </c>
       <c r="BH48" s="8">
         <f>BI48-BG48</f>
-        <v>5013932</v>
+        <v>5014022</v>
       </c>
       <c r="BI48" s="7">
         <f>SUM(BI10:BI47)</f>
-        <v>12006313</v>
+        <v>12006403</v>
       </c>
       <c r="BJ48" s="6">
         <f>BI48/BF48</f>
-        <v>0.99493677725292073</v>
+        <v>0.99494423535516685</v>
       </c>
     </row>
   </sheetData>
